--- a/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>JOB</t>
   </si>
@@ -656,403 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>34300</v>
+      </c>
+      <c r="F8" s="3">
         <v>38200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>38900</v>
-      </c>
-      <c r="F8" s="3">
-        <v>41100</v>
-      </c>
-      <c r="G8" s="3">
-        <v>41500</v>
       </c>
       <c r="H8" s="3">
         <v>41100</v>
       </c>
       <c r="I8" s="3">
+        <v>41500</v>
+      </c>
+      <c r="J8" s="3">
+        <v>41100</v>
+      </c>
+      <c r="K8" s="3">
         <v>39600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>42800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>41500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>38100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>34700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>34600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>31000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>26600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>34700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>37600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>38900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>38100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>36200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>38500</v>
-      </c>
-      <c r="W8" s="3">
-        <v>39900</v>
-      </c>
-      <c r="X8" s="3">
-        <v>40300</v>
       </c>
       <c r="Y8" s="3">
         <v>39900</v>
       </c>
       <c r="Z8" s="3">
+        <v>40300</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>39900</v>
+      </c>
+      <c r="AB8" s="3">
         <v>45200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>46400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>46100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>21500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>21000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>22700</v>
+      </c>
+      <c r="F9" s="3">
         <v>24500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>25600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>26800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>26400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>24600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>25100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>27300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>26200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>24200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>23800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>22100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>20500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>16900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>22800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>25000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>25600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>24500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>24500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>25800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>25100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>25500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>26200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>29500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>29500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>29000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>15900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>15600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F10" s="3">
         <v>13700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>13300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>14300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>15100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>16500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>14500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>15500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>15300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>13900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>10900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>12500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>10500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>9700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>11900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>12600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>13300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>13600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>11700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>12700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>14800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>14800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>13700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>15700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>16900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>17100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>5600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>5400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1109,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1173,8 +1200,14 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,97 +1295,109 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E14" s="3">
+        <v>700</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-14100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-1100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>2200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>9900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-10800</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>1300</v>
-      </c>
-      <c r="R14" s="3">
-        <v>400</v>
       </c>
       <c r="S14" s="3">
         <v>1300</v>
       </c>
       <c r="T14" s="3">
+        <v>400</v>
+      </c>
+      <c r="U14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="V14" s="3">
         <v>4900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>1200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>200</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>3200</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
       </c>
       <c r="AE14" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1372,10 +1417,10 @@
         <v>800</v>
       </c>
       <c r="I15" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="J15" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="K15" s="3">
         <v>1100</v>
@@ -1390,16 +1435,16 @@
         <v>1100</v>
       </c>
       <c r="O15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q15" s="3">
         <v>1200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>1500</v>
-      </c>
-      <c r="R15" s="3">
-        <v>1500</v>
       </c>
       <c r="S15" s="3">
         <v>1500</v>
@@ -1426,22 +1471,28 @@
         <v>1500</v>
       </c>
       <c r="AA15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AC15" s="3">
         <v>1300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>1700</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>400</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>400</v>
       </c>
       <c r="AE15" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1521,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>34800</v>
+      </c>
+      <c r="F17" s="3">
         <v>37100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>38200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>40400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>41700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>38300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>38500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>26100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>38000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>38500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>33800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>32700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>40600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>16000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>37000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>37700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>39200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>41900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>37000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>38500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>38900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>39700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>39800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>43800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>46100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>49500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>21200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>20500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F18" s="3">
         <v>1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>2800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>16700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>3500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-9600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>10600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-2300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-3800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-800</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
         <v>1000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1400</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>300</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-3400</v>
       </c>
       <c r="AC18" s="3">
         <v>300</v>
       </c>
       <c r="AD18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF18" s="3">
         <v>500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,13 +1746,15 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
         <v>100</v>
@@ -1696,10 +1763,10 @@
         <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1768,99 +1835,111 @@
         <v>0</v>
       </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>500</v>
+      </c>
+      <c r="F21" s="3">
         <v>2100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>1600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>3600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>2300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>17800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>4600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>3100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-8400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>11800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-2300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>2500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>2100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>3000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1889,37 +1968,37 @@
         <v>100</v>
       </c>
       <c r="L22" s="3">
+        <v>100</v>
+      </c>
+      <c r="M22" s="3">
+        <v>100</v>
+      </c>
+      <c r="N22" s="3">
         <v>500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>2500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>2700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>2600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>3300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>3100</v>
-      </c>
-      <c r="R22" s="3">
-        <v>3200</v>
-      </c>
-      <c r="S22" s="3">
-        <v>3200</v>
       </c>
       <c r="T22" s="3">
         <v>3200</v>
       </c>
       <c r="U22" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="V22" s="3">
-        <v>2900</v>
+        <v>3200</v>
       </c>
       <c r="W22" s="3">
         <v>3100</v>
@@ -1928,206 +2007,224 @@
         <v>2900</v>
       </c>
       <c r="Y22" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AA22" s="3">
         <v>2200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>3300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>2900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>2400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F23" s="3">
         <v>1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>16600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>3400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-12200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>7300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-5400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-3400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-3600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-6900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-3900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-2900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-2100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F24" s="3">
         <v>-6800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>100</v>
-      </c>
-      <c r="G24" s="3">
-        <v>500</v>
       </c>
       <c r="H24" s="3">
         <v>100</v>
       </c>
       <c r="I24" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2312,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>200</v>
+      </c>
+      <c r="F26" s="3">
         <v>7900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>2600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>16700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>3000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-12600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>7200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-5400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-3600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-3600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-6800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-3900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-3500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>3700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>200</v>
+      </c>
+      <c r="F27" s="3">
         <v>7900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>2600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>16700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>3000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-12600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>31700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-5400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-3600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-6800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-3900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-3500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>3700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2597,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2526,11 +2647,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2544,23 +2665,23 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>400</v>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3" t="s">
+      <c r="Y29" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z29" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>400</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>400</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2571,8 +2692,14 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2787,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,13 +2882,19 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
         <v>-100</v>
@@ -2764,10 +2903,10 @@
         <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -2836,99 +2975,111 @@
         <v>0</v>
       </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>200</v>
+      </c>
+      <c r="F33" s="3">
         <v>7900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>2600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>16700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>3000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-12600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>31700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-5400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-3600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-6800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-3900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-3500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>3700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3167,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>200</v>
+      </c>
+      <c r="F35" s="3">
         <v>7900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>2600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>16700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>3000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-12600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>31700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-5400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-3600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-6800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-3900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-3500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>3700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3401,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3436,105 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>22500</v>
+      </c>
+      <c r="F41" s="3">
         <v>20700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>20100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>18500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>18800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>17500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>14200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>12100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>9900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>14300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>14100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>14100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>16600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>4100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>4200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>2800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>3500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>3200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>3500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>2800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>2900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>2200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,97 +3622,109 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>18300</v>
+      </c>
+      <c r="F43" s="3">
         <v>19900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>20400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>20300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>22800</v>
-      </c>
-      <c r="H43" s="3">
-        <v>21200</v>
-      </c>
-      <c r="I43" s="3">
-        <v>21200</v>
       </c>
       <c r="J43" s="3">
         <v>21200</v>
       </c>
       <c r="K43" s="3">
+        <v>21200</v>
+      </c>
+      <c r="L43" s="3">
+        <v>21200</v>
+      </c>
+      <c r="M43" s="3">
         <v>23100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>20300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>19000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>18600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>16000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>13700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>17300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>20200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>20800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>20400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>20000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>19000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>20800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>21200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>20600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>22700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>23200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>24000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>13100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>12600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,13 +3812,19 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>700</v>
+        <v>1300</v>
       </c>
       <c r="E45" s="3">
         <v>800</v>
@@ -3636,171 +3833,183 @@
         <v>700</v>
       </c>
       <c r="G45" s="3">
+        <v>800</v>
+      </c>
+      <c r="H45" s="3">
+        <v>700</v>
+      </c>
+      <c r="I45" s="3">
         <v>600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>800</v>
-      </c>
-      <c r="M45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="N45" s="3">
-        <v>900</v>
       </c>
       <c r="O45" s="3">
         <v>1400</v>
       </c>
       <c r="P45" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S45" s="3">
         <v>1600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>2200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>2800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>2400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>2500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>2300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>3000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>2500</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>1600</v>
       </c>
       <c r="AE45" s="3">
         <v>1500</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>41700</v>
+      </c>
+      <c r="F46" s="3">
         <v>41400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>41300</v>
-      </c>
-      <c r="F46" s="3">
-        <v>39500</v>
-      </c>
-      <c r="G46" s="3">
-        <v>42200</v>
       </c>
       <c r="H46" s="3">
         <v>39500</v>
       </c>
       <c r="I46" s="3">
+        <v>42200</v>
+      </c>
+      <c r="J46" s="3">
+        <v>39500</v>
+      </c>
+      <c r="K46" s="3">
         <v>36200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>34200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>33700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>28500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>34700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>33600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>31500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>31700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>21200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>23700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>27100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>27400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>25100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>25000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>26200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>25700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>25300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>27500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>29000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>29400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>16200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>16400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>15600</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3888,73 +4097,79 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F48" s="3">
         <v>4900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>5000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>4100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>4000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>4200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>4600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>4700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>5100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>5500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>5500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>6300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>6300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>900</v>
-      </c>
-      <c r="T48" s="3">
-        <v>800</v>
-      </c>
-      <c r="U48" s="3">
-        <v>800</v>
       </c>
       <c r="V48" s="3">
         <v>800</v>
       </c>
       <c r="W48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="X48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="Y48" s="3">
         <v>900</v>
@@ -3969,105 +4184,117 @@
         <v>900</v>
       </c>
       <c r="AC48" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD48" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE48" s="3">
         <v>500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>69700</v>
+      </c>
+      <c r="F49" s="3">
         <v>70400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>71100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>71900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>72600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>73300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>74000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>75000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>78200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>79200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>80200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>81200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>82300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>92300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>93400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>94800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>96200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>97600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>103300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>104700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>106100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>107500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>108900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>110200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>111600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>110300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>28900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>29300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4382,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,67 +4477,73 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F52" s="3">
         <v>7000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>700</v>
-      </c>
-      <c r="G52" s="3">
-        <v>800</v>
-      </c>
-      <c r="H52" s="3">
-        <v>800</v>
       </c>
       <c r="I52" s="3">
         <v>800</v>
       </c>
       <c r="J52" s="3">
+        <v>800</v>
+      </c>
+      <c r="K52" s="3">
+        <v>800</v>
+      </c>
+      <c r="L52" s="3">
         <v>1000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>400</v>
-      </c>
-      <c r="S52" s="3">
-        <v>400</v>
-      </c>
-      <c r="T52" s="3">
-        <v>600</v>
       </c>
       <c r="U52" s="3">
         <v>400</v>
       </c>
       <c r="V52" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="W52" s="3">
         <v>400</v>
@@ -4313,28 +4552,34 @@
         <v>400</v>
       </c>
       <c r="Y52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Z52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AA52" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AB52" s="3">
         <v>300</v>
       </c>
       <c r="AC52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AD52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4667,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>117600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>123500</v>
+      </c>
+      <c r="F54" s="3">
         <v>123700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>118100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>116200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>119600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>117800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>115600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>114900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>117600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>113300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>120200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>120500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>120000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>129800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>121200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>125200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>124500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>126300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>129600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>130900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>133600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>134400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>135100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>139000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>141800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>141000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>45700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>46300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>45900</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4801,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,115 +4836,123 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="E57" s="3">
-        <v>3400</v>
+        <v>2800</v>
       </c>
       <c r="F57" s="3">
         <v>2900</v>
       </c>
       <c r="G57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I57" s="3">
         <v>3000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>2500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>3700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>9100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>3900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>2900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>2500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>2000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>2000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>2100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>3200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>1400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>1600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>100</v>
+      </c>
+      <c r="F58" s="3">
         <v>200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>200</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="H58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -4693,248 +4960,266 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>16700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>11000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>8800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>5600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>2200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>7900</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>1200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>5700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>3900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>2200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>3200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>2400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>17200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>16800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>15000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>12600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>14000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>8500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>10100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F59" s="3">
         <v>7100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>7800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>8100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>12600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>10400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>11600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>11300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>12200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>10600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>15400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>14600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>13900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>14400</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>9200</v>
-      </c>
-      <c r="R59" s="3">
-        <v>9300</v>
       </c>
       <c r="S59" s="3">
         <v>9200</v>
       </c>
       <c r="T59" s="3">
+        <v>9300</v>
+      </c>
+      <c r="U59" s="3">
+        <v>9200</v>
+      </c>
+      <c r="V59" s="3">
         <v>2900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>7900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>7400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>8200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>8600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>7400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>9800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>13800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>12500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>5000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>4800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10100</v>
+        <v>8900</v>
       </c>
       <c r="E60" s="3">
         <v>11400</v>
       </c>
       <c r="F60" s="3">
+        <v>10100</v>
+      </c>
+      <c r="G60" s="3">
+        <v>11400</v>
+      </c>
+      <c r="H60" s="3">
         <v>11000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>15600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>12900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>13300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>13600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>31200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>23400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>26000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>22100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>18200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>24800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>11700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>13400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>18600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>15900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>14000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>13500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>13100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>27800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>26300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>26900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>19500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>27900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>14800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>16400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4942,14 +5227,14 @@
         <v>200</v>
       </c>
       <c r="E61" s="3">
+        <v>200</v>
+      </c>
+      <c r="F61" s="3">
+        <v>200</v>
+      </c>
+      <c r="G61" s="3">
         <v>300</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -4963,156 +5248,168 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>7000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>62500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>65000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>67400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>60700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>74900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>72500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>68200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>69800</v>
-      </c>
-      <c r="U61" s="3">
-        <v>69900</v>
-      </c>
-      <c r="V61" s="3">
-        <v>68800</v>
       </c>
       <c r="W61" s="3">
         <v>69900</v>
       </c>
       <c r="X61" s="3">
+        <v>68800</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>69900</v>
+      </c>
+      <c r="Z61" s="3">
         <v>55000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>56000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>58500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>67600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>59000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>4900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>4800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F62" s="3">
         <v>3000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>3700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>3100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>3000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>3200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>3500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>3700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>5700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>5200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>5800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>6000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>7100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>4600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>4900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>900</v>
-      </c>
-      <c r="T62" s="3">
-        <v>1200</v>
-      </c>
-      <c r="U62" s="3">
-        <v>1200</v>
       </c>
       <c r="V62" s="3">
         <v>1200</v>
       </c>
       <c r="W62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y62" s="3">
         <v>700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>4700</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>200</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>200</v>
       </c>
       <c r="AE62" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5497,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5592,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5687,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>14200</v>
+      </c>
+      <c r="F66" s="3">
         <v>13300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>15300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>14100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>18600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>16200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>16800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>17300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>36800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>35600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>94300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>93100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>92600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>90100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>91500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>90900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>87700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>86900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>85100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>83500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>83700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>84500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>84100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>86500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>88400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>91600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>19800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>21500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5821,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5912,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6007,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5723,16 +6058,16 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>27700</v>
       </c>
-      <c r="R70" s="3">
+      <c r="T70" s="3">
         <v>27700</v>
-      </c>
-      <c r="S70" s="3">
-        <v>27600</v>
-      </c>
-      <c r="T70" s="3">
-        <v>27600</v>
       </c>
       <c r="U70" s="3">
         <v>27600</v>
@@ -5741,34 +6076,40 @@
         <v>27600</v>
       </c>
       <c r="W70" s="3">
-        <v>28800</v>
+        <v>27600</v>
       </c>
       <c r="X70" s="3">
-        <v>28800</v>
+        <v>27600</v>
       </c>
       <c r="Y70" s="3">
         <v>28800</v>
       </c>
       <c r="Z70" s="3">
-        <v>29300</v>
+        <v>28800</v>
       </c>
       <c r="AA70" s="3">
-        <v>29300</v>
+        <v>28800</v>
       </c>
       <c r="AB70" s="3">
         <v>29300</v>
       </c>
       <c r="AC70" s="3">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="AD70" s="3">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6197,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-9700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-10400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-11000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-10300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-12900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-14000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-30600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-33600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-32700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-31000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-30700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-49800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-44300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-40800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-37200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-30400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-26500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-23000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-22000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-20100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-17200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-15500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-19200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-13200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-13000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6387,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6482,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6577,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>106300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>109300</v>
+      </c>
+      <c r="F76" s="3">
         <v>110400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>102800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>102000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>101000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>101600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>98800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>97600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>80800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>77600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>25900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>27400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>27400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>39700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>2000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>6600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>9200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>11900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>16900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>19900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>21100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>21100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>22200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>23200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>24100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>20100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>25800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>24800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6767,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>200</v>
+      </c>
+      <c r="F81" s="3">
         <v>7900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>2600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>16700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>3000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-12600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>31700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-5400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-3600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-6800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-3900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-3500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>3700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +7001,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6627,10 +7024,10 @@
         <v>800</v>
       </c>
       <c r="I83" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="J83" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="K83" s="3">
         <v>1100</v>
@@ -6645,16 +7042,16 @@
         <v>1100</v>
       </c>
       <c r="O83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q83" s="3">
         <v>1200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>1500</v>
-      </c>
-      <c r="R83" s="3">
-        <v>1500</v>
       </c>
       <c r="S83" s="3">
         <v>1500</v>
@@ -6681,22 +7078,28 @@
         <v>1500</v>
       </c>
       <c r="AA83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AC83" s="3">
         <v>1300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>1700</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>400</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>400</v>
       </c>
       <c r="AE83" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7187,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7282,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7377,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7472,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7567,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F89" s="3">
         <v>1200</v>
       </c>
-      <c r="E89" s="3">
-        <v>1800</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J89" s="3">
         <v>3500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>2300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>2600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>100</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-2500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>2300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-1500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7701,10 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7274,10 +7715,10 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
@@ -7295,10 +7736,10 @@
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -7310,22 +7751,22 @@
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
       <c r="W91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -7334,25 +7775,31 @@
         <v>-100</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7887,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7982,14 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7541,10 +8000,10 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H94" s="3">
         <v>-100</v>
@@ -7562,10 +8021,10 @@
         <v>-100</v>
       </c>
       <c r="M94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -7577,22 +8036,22 @@
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
       <c r="W94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -7601,25 +8060,31 @@
         <v>-100</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-24800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +8116,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +8207,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8302,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8397,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,23 +8492,29 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
@@ -8037,67 +8528,73 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-4400</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>11900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>2200</v>
-      </c>
-      <c r="U100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V100" s="3">
-        <v>-500</v>
       </c>
       <c r="W100" s="3">
         <v>-100</v>
       </c>
       <c r="X100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-800</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>-900</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>1100</v>
       </c>
       <c r="AA100" s="3">
         <v>-900</v>
       </c>
       <c r="AB100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AD100" s="3">
         <v>26700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,93 +8682,105 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F102" s="3">
         <v>600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>3400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>2000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>2200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>2600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-6900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>100</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-2500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>14200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>1400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>1300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>JOB</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E8" s="3">
         <v>30600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>34300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>38200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>38900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>41100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>41500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>41100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>39600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>42800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>41500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>38100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>34700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>31000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>26600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>37600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>38900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>38100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>36200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>38500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>39900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>40300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>39900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>45200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>46400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>46100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>21500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>21000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E9" s="3">
         <v>20900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>22700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>24500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>25600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>26800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>24600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>25100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>27300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>24200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>23800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>22100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>20500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>22800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>25000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>25600</v>
-      </c>
-      <c r="V9" s="3">
-        <v>24500</v>
       </c>
       <c r="W9" s="3">
         <v>24500</v>
       </c>
       <c r="X9" s="3">
+        <v>24500</v>
+      </c>
+      <c r="Y9" s="3">
         <v>25800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>25100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>25500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>26200</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>29500</v>
       </c>
       <c r="AC9" s="3">
         <v>29500</v>
       </c>
       <c r="AD9" s="3">
+        <v>29500</v>
+      </c>
+      <c r="AE9" s="3">
         <v>29000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>15900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>15600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E10" s="3">
         <v>9700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>14300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>15100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>16500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>14500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>15500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>12500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>12600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>13300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>13600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>11700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>12700</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>14800</v>
       </c>
       <c r="Z10" s="3">
         <v>14800</v>
       </c>
       <c r="AA10" s="3">
+        <v>14800</v>
+      </c>
+      <c r="AB10" s="3">
         <v>13700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>15700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>16900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>17100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1310,94 +1330,97 @@
         <v>500</v>
       </c>
       <c r="E14" s="3">
+        <v>500</v>
+      </c>
+      <c r="F14" s="3">
         <v>700</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-14100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-1100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>9900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-10800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>4900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>200</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>3200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>100</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1423,7 +1446,7 @@
         <v>800</v>
       </c>
       <c r="K15" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="L15" s="3">
         <v>1100</v>
@@ -1441,13 +1464,13 @@
         <v>1100</v>
       </c>
       <c r="Q15" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="R15" s="3">
         <v>1200</v>
       </c>
       <c r="S15" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="T15" s="3">
         <v>1500</v>
@@ -1477,13 +1500,13 @@
         <v>1500</v>
       </c>
       <c r="AC15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AD15" s="3">
         <v>1300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1700</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>400</v>
       </c>
       <c r="AF15" s="3">
         <v>400</v>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E17" s="3">
         <v>32300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>37100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>38200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>40400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>41700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>38300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>38500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>26100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>38000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>38500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>33800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>32700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>40600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>16000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>37000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>37700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>39200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>41900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>37000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>38500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>38900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>39700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>39800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>43800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>46100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>49500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>21200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>20500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1100</v>
-      </c>
-      <c r="G18" s="3">
-        <v>700</v>
       </c>
       <c r="H18" s="3">
         <v>700</v>
       </c>
       <c r="I18" s="3">
+        <v>700</v>
+      </c>
+      <c r="J18" s="3">
         <v>-200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>16700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-800</v>
       </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
       <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
         <v>1000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>300</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>500</v>
       </c>
       <c r="AG18" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,16 +1781,17 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
-      </c>
-      <c r="E20" s="3">
-        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
@@ -1769,7 +1803,7 @@
         <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1841,105 +1875,111 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1600</v>
       </c>
       <c r="H21" s="3">
         <v>1600</v>
       </c>
       <c r="I21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J21" s="3">
         <v>600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>17800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-8400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1974,25 +2014,25 @@
         <v>100</v>
       </c>
       <c r="N22" s="3">
+        <v>100</v>
+      </c>
+      <c r="O22" s="3">
         <v>500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3100</v>
-      </c>
-      <c r="T22" s="3">
-        <v>3200</v>
       </c>
       <c r="U22" s="3">
         <v>3200</v>
@@ -2001,230 +2041,239 @@
         <v>3200</v>
       </c>
       <c r="W22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="X22" s="3">
         <v>3100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>3100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>3300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2400</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>400</v>
       </c>
       <c r="AF22" s="3">
         <v>400</v>
       </c>
       <c r="AG22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1100</v>
-      </c>
-      <c r="G23" s="3">
-        <v>700</v>
       </c>
       <c r="H23" s="3">
         <v>700</v>
       </c>
       <c r="I23" s="3">
+        <v>700</v>
+      </c>
+      <c r="J23" s="3">
         <v>-300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>16600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-12200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-6800</v>
-      </c>
-      <c r="G24" s="3">
-        <v>100</v>
       </c>
       <c r="H24" s="3">
         <v>100</v>
       </c>
       <c r="I24" s="3">
+        <v>100</v>
+      </c>
+      <c r="J24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>-100</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-6400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>200</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>100</v>
       </c>
       <c r="AF24" s="3">
         <v>100</v>
       </c>
       <c r="AG24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7900</v>
-      </c>
-      <c r="G26" s="3">
-        <v>700</v>
       </c>
       <c r="H26" s="3">
         <v>700</v>
       </c>
       <c r="I26" s="3">
+        <v>700</v>
+      </c>
+      <c r="J26" s="3">
         <v>-800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>16700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-12600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5400</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-3600</v>
       </c>
       <c r="U26" s="3">
         <v>-3600</v>
       </c>
       <c r="V26" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="W26" s="3">
         <v>-6800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>700</v>
       </c>
       <c r="H27" s="3">
         <v>700</v>
       </c>
       <c r="I27" s="3">
+        <v>700</v>
+      </c>
+      <c r="J27" s="3">
         <v>-800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-12600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>31700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5400</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-3600</v>
       </c>
       <c r="U27" s="3">
         <v>-3600</v>
       </c>
       <c r="V27" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="W27" s="3">
         <v>-6800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2653,8 +2714,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2671,20 +2732,20 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>400</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>400</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,16 +2955,19 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>-100</v>
@@ -2909,7 +2979,7 @@
         <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -2981,105 +3051,111 @@
         <v>0</v>
       </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7900</v>
-      </c>
-      <c r="G33" s="3">
-        <v>700</v>
       </c>
       <c r="H33" s="3">
         <v>700</v>
       </c>
       <c r="I33" s="3">
+        <v>700</v>
+      </c>
+      <c r="J33" s="3">
         <v>-800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-12600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>31700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5400</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-3600</v>
       </c>
       <c r="U33" s="3">
         <v>-3600</v>
       </c>
       <c r="V33" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="W33" s="3">
         <v>-6800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7900</v>
-      </c>
-      <c r="G35" s="3">
-        <v>700</v>
       </c>
       <c r="H35" s="3">
         <v>700</v>
       </c>
       <c r="I35" s="3">
+        <v>700</v>
+      </c>
+      <c r="J35" s="3">
         <v>-800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-12600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>31700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5400</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-3600</v>
       </c>
       <c r="U35" s="3">
         <v>-3600</v>
       </c>
       <c r="V35" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="W35" s="3">
         <v>-6800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E41" s="3">
         <v>19900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14300</v>
-      </c>
-      <c r="P41" s="3">
-        <v>14100</v>
       </c>
       <c r="Q41" s="3">
         <v>14100</v>
       </c>
       <c r="R41" s="3">
+        <v>14100</v>
+      </c>
+      <c r="S41" s="3">
         <v>16600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,31 +3718,34 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E43" s="3">
         <v>15900</v>
       </c>
-      <c r="E43" s="3">
-        <v>18300</v>
-      </c>
       <c r="F43" s="3">
+        <v>18500</v>
+      </c>
+      <c r="G43" s="3">
         <v>19900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>20400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>20300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>22800</v>
-      </c>
-      <c r="J43" s="3">
-        <v>21200</v>
       </c>
       <c r="K43" s="3">
         <v>21200</v>
@@ -3661,70 +3754,73 @@
         <v>21200</v>
       </c>
       <c r="M43" s="3">
+        <v>21200</v>
+      </c>
+      <c r="N43" s="3">
         <v>23100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>20300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>19000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>18600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>16000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>17300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>20200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>20800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>20400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>20000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>19000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>20800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>21200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>20600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>22700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>23200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>24000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>13100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>12600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,198 +3914,207 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E45" s="3">
         <v>1300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>600</v>
-      </c>
-      <c r="J45" s="3">
-        <v>800</v>
       </c>
       <c r="K45" s="3">
         <v>800</v>
       </c>
       <c r="L45" s="3">
+        <v>800</v>
+      </c>
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>900</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>1400</v>
       </c>
       <c r="R45" s="3">
         <v>1400</v>
       </c>
       <c r="S45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T45" s="3">
         <v>1600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E46" s="3">
         <v>37000</v>
       </c>
-      <c r="E46" s="3">
-        <v>41700</v>
-      </c>
       <c r="F46" s="3">
+        <v>41800</v>
+      </c>
+      <c r="G46" s="3">
         <v>41400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>41300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>39500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>42200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>39500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>36200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>34200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>33700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>28500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>34700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>33600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>31500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>31700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>21200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>23700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>27100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>27400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>25100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>25000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>26200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>25700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>25300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>27500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>29000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>29400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>16200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>16400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>15600</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4103,67 +4208,70 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E48" s="3">
         <v>4100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4600</v>
-      </c>
-      <c r="L48" s="3">
-        <v>4700</v>
       </c>
       <c r="M48" s="3">
         <v>4700</v>
       </c>
       <c r="N48" s="3">
+        <v>4700</v>
+      </c>
+      <c r="O48" s="3">
         <v>4400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5100</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>5500</v>
       </c>
       <c r="R48" s="3">
         <v>5500</v>
       </c>
       <c r="S48" s="3">
-        <v>6300</v>
+        <v>5500</v>
       </c>
       <c r="T48" s="3">
         <v>6300</v>
       </c>
       <c r="U48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="V48" s="3">
         <v>900</v>
-      </c>
-      <c r="V48" s="3">
-        <v>800</v>
       </c>
       <c r="W48" s="3">
         <v>800</v>
@@ -4172,7 +4280,7 @@
         <v>800</v>
       </c>
       <c r="Y48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="Z48" s="3">
         <v>900</v>
@@ -4190,111 +4298,117 @@
         <v>900</v>
       </c>
       <c r="AE48" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AF48" s="3">
         <v>500</v>
       </c>
       <c r="AG48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH48" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>68300</v>
+      </c>
+      <c r="E49" s="3">
         <v>69000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>69700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>70400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>71100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>71900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>72600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>73300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>74000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>75000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>78200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>79200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>80200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>81200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>82300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>92300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>93400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>94800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>96200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>97600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>103300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>104700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>106100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>107500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>108900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>110200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>111600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>110300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>28900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>29300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,28 +4600,31 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E52" s="3">
         <v>7500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>700</v>
       </c>
       <c r="H52" s="3">
         <v>700</v>
       </c>
       <c r="I52" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="J52" s="3">
         <v>800</v>
@@ -4513,40 +4633,40 @@
         <v>800</v>
       </c>
       <c r="L52" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="M52" s="3">
         <v>1000</v>
       </c>
       <c r="N52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O52" s="3">
         <v>1100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>700</v>
-      </c>
-      <c r="R52" s="3">
-        <v>300</v>
       </c>
       <c r="S52" s="3">
         <v>300</v>
       </c>
       <c r="T52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="U52" s="3">
         <v>400</v>
       </c>
       <c r="V52" s="3">
+        <v>400</v>
+      </c>
+      <c r="W52" s="3">
         <v>600</v>
-      </c>
-      <c r="W52" s="3">
-        <v>400</v>
       </c>
       <c r="X52" s="3">
         <v>400</v>
@@ -4558,10 +4678,10 @@
         <v>400</v>
       </c>
       <c r="AA52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AB52" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AC52" s="3">
         <v>300</v>
@@ -4570,7 +4690,7 @@
         <v>300</v>
       </c>
       <c r="AE52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AF52" s="3">
         <v>0</v>
@@ -4578,8 +4698,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>117000</v>
+      </c>
+      <c r="E54" s="3">
         <v>117600</v>
       </c>
-      <c r="E54" s="3">
-        <v>123500</v>
-      </c>
       <c r="F54" s="3">
+        <v>123600</v>
+      </c>
+      <c r="G54" s="3">
         <v>123700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>118100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>116200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>119600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>117800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>115600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>114900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>117600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>113300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>120200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>120500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>120000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>129800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>121200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>125200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>124500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>126300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>129600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>130900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>133600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>134400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>135100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>139000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>141800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>141000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>45700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>46300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>45900</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,8 +4968,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4847,94 +4978,97 @@
         <v>2500</v>
       </c>
       <c r="E57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F57" s="3">
         <v>2800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2500</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>2000</v>
       </c>
       <c r="AA57" s="3">
         <v>2000</v>
       </c>
       <c r="AB57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AC57" s="3">
         <v>2100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4945,17 +5079,17 @@
         <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G58" s="3">
         <v>200</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="H58" s="3">
+        <v>200</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -4966,260 +5100,269 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>16700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>8800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7900</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>1200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>17200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>16800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>15000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>12600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>14000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>8500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>10100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E59" s="3">
         <v>6300</v>
       </c>
-      <c r="E59" s="3">
-        <v>8500</v>
-      </c>
       <c r="F59" s="3">
+        <v>10200</v>
+      </c>
+      <c r="G59" s="3">
         <v>7100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>7400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>13800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>12500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E60" s="3">
         <v>8900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
+        <v>11500</v>
+      </c>
+      <c r="G60" s="3">
+        <v>10100</v>
+      </c>
+      <c r="H60" s="3">
         <v>11400</v>
       </c>
-      <c r="F60" s="3">
-        <v>10100</v>
-      </c>
-      <c r="G60" s="3">
-        <v>11400</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>31200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>23400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>24800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>18600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>15900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>14000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>13500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>13100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>27800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>26300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>26900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>19500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>27900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>14800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>16400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5233,11 +5376,11 @@
         <v>200</v>
       </c>
       <c r="G61" s="3">
+        <v>200</v>
+      </c>
+      <c r="H61" s="3">
         <v>300</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -5254,126 +5397,129 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>7000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>62500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>65000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>67400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>60700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>74900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>72500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>68200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>69800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>69900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>68800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>69900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>55000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>56000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>58500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>67600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>59000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>2600</v>
       </c>
       <c r="F62" s="3">
         <v>3000</v>
       </c>
       <c r="G62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H62" s="3">
         <v>3700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4600</v>
-      </c>
-      <c r="S62" s="3">
-        <v>4900</v>
       </c>
       <c r="T62" s="3">
         <v>4900</v>
       </c>
       <c r="U62" s="3">
+        <v>4900</v>
+      </c>
+      <c r="V62" s="3">
         <v>900</v>
-      </c>
-      <c r="V62" s="3">
-        <v>1200</v>
       </c>
       <c r="W62" s="3">
         <v>1200</v>
@@ -5382,25 +5528,25 @@
         <v>1200</v>
       </c>
       <c r="Y62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z62" s="3">
         <v>700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4700</v>
-      </c>
-      <c r="AE62" s="3">
-        <v>200</v>
       </c>
       <c r="AF62" s="3">
         <v>200</v>
@@ -5408,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E66" s="3">
         <v>11300</v>
       </c>
-      <c r="E66" s="3">
-        <v>14200</v>
-      </c>
       <c r="F66" s="3">
+        <v>14300</v>
+      </c>
+      <c r="G66" s="3">
         <v>13300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>17300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>36800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>35600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>94300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>93100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>92600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>90100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>91500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>90900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>87700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>86900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>85100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>83500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>83700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>84500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>84100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>86500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>88400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>91600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>21500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6064,13 +6232,13 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
-        <v>27700</v>
+        <v>0</v>
       </c>
       <c r="T70" s="3">
         <v>27700</v>
       </c>
       <c r="U70" s="3">
-        <v>27600</v>
+        <v>27700</v>
       </c>
       <c r="V70" s="3">
         <v>27600</v>
@@ -6082,7 +6250,7 @@
         <v>27600</v>
       </c>
       <c r="Y70" s="3">
-        <v>28800</v>
+        <v>27600</v>
       </c>
       <c r="Z70" s="3">
         <v>28800</v>
@@ -6091,7 +6259,7 @@
         <v>28800</v>
       </c>
       <c r="AB70" s="3">
-        <v>29300</v>
+        <v>28800</v>
       </c>
       <c r="AC70" s="3">
         <v>29300</v>
@@ -6100,7 +6268,7 @@
         <v>29300</v>
       </c>
       <c r="AE70" s="3">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="AF70" s="3">
         <v>0</v>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-9700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-10400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-11000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-10300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-12900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-14000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-30600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-33600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-32700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-31000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-30700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-18100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-49800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-44300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-40800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-37200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-30400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-26500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-23000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-22000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-20100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-17200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-15500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-19200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-13200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-13000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>105500</v>
+      </c>
+      <c r="E76" s="3">
         <v>106300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>109300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>110400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>102800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>102000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>101000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>101600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>98800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>97600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>80800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>77600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>25900</v>
-      </c>
-      <c r="P76" s="3">
-        <v>27400</v>
       </c>
       <c r="Q76" s="3">
         <v>27400</v>
       </c>
       <c r="R76" s="3">
+        <v>27400</v>
+      </c>
+      <c r="S76" s="3">
         <v>39700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>19900</v>
-      </c>
-      <c r="Y76" s="3">
-        <v>21100</v>
       </c>
       <c r="Z76" s="3">
         <v>21100</v>
       </c>
       <c r="AA76" s="3">
+        <v>21100</v>
+      </c>
+      <c r="AB76" s="3">
         <v>22200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>23200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>24100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>20100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>25800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>24800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7900</v>
-      </c>
-      <c r="G81" s="3">
-        <v>700</v>
       </c>
       <c r="H81" s="3">
         <v>700</v>
       </c>
       <c r="I81" s="3">
+        <v>700</v>
+      </c>
+      <c r="J81" s="3">
         <v>-800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-12600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>31700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5400</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-3600</v>
       </c>
       <c r="U81" s="3">
         <v>-3600</v>
       </c>
       <c r="V81" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="W81" s="3">
         <v>-6800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7030,7 +7229,7 @@
         <v>800</v>
       </c>
       <c r="K83" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="L83" s="3">
         <v>1100</v>
@@ -7048,13 +7247,13 @@
         <v>1100</v>
       </c>
       <c r="Q83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="R83" s="3">
         <v>1200</v>
       </c>
       <c r="S83" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="T83" s="3">
         <v>1500</v>
@@ -7084,13 +7283,13 @@
         <v>1500</v>
       </c>
       <c r="AC83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AD83" s="3">
         <v>1300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1700</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>400</v>
       </c>
       <c r="AF83" s="3">
         <v>400</v>
@@ -7098,8 +7297,11 @@
       <c r="AG83" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>100</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
         <v>-2500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-600</v>
-      </c>
-      <c r="X89" s="3">
-        <v>800</v>
       </c>
       <c r="Y89" s="3">
         <v>800</v>
       </c>
       <c r="Z89" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA89" s="3">
         <v>500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7721,7 +7942,7 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
@@ -7742,7 +7963,7 @@
         <v>-100</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -7757,13 +7978,13 @@
         <v>0</v>
       </c>
       <c r="T91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U91" s="3">
         <v>-100</v>
       </c>
       <c r="V91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -7772,23 +7993,23 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB91" s="3">
         <v>-100</v>
       </c>
       <c r="AC91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
@@ -7796,10 +8017,13 @@
         <v>0</v>
       </c>
       <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,8 +8215,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8006,7 +8236,7 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I94" s="3">
         <v>-100</v>
@@ -8027,7 +8257,7 @@
         <v>-100</v>
       </c>
       <c r="O94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -8042,13 +8272,13 @@
         <v>0</v>
       </c>
       <c r="T94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U94" s="3">
         <v>-100</v>
       </c>
       <c r="V94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -8057,34 +8287,37 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB94" s="3">
         <v>-100</v>
       </c>
       <c r="AC94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-24800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-500</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>-100</v>
       </c>
       <c r="AG94" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,26 +8741,29 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1600</v>
+        <v>0</v>
       </c>
       <c r="E100" s="3">
         <v>-1600</v>
       </c>
       <c r="F100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G100" s="3">
         <v>-500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
@@ -8534,11 +8780,11 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-4400</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
@@ -8546,55 +8792,58 @@
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>11900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>26700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8688,99 +8937,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>100</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-2500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>14200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>JOB</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E8" s="3">
         <v>28100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>30600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>34300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>38200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>38900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>41100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>41500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>41100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>39600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>42800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>41500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>38100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>34600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>31000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>26600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>37600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>38900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>38100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>36200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>38500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>39900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>40300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>39900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>45200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>46400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>46100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>21500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>21000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E9" s="3">
         <v>19300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>22700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>24500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>25600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>26400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>24600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>25100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>27300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>24200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>23800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>22100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>20500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>16900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>22800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>25000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>25600</v>
-      </c>
-      <c r="W9" s="3">
-        <v>24500</v>
       </c>
       <c r="X9" s="3">
         <v>24500</v>
       </c>
       <c r="Y9" s="3">
+        <v>24500</v>
+      </c>
+      <c r="Z9" s="3">
         <v>25800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>25100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>25500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>26200</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>29500</v>
       </c>
       <c r="AD9" s="3">
         <v>29500</v>
       </c>
       <c r="AE9" s="3">
+        <v>29500</v>
+      </c>
+      <c r="AF9" s="3">
         <v>29000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>15900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>15600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E10" s="3">
         <v>8800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>11600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>14300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>15100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>16500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>12500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>10500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>12600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>13300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>13600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>11700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>12700</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>14800</v>
       </c>
       <c r="AA10" s="3">
         <v>14800</v>
       </c>
       <c r="AB10" s="3">
+        <v>14800</v>
+      </c>
+      <c r="AC10" s="3">
         <v>13700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>15700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>16900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>17100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>5400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,106 +1338,112 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>500</v>
+        <v>20500</v>
       </c>
       <c r="E14" s="3">
         <v>500</v>
       </c>
       <c r="F14" s="3">
+        <v>500</v>
+      </c>
+      <c r="G14" s="3">
         <v>700</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-14100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-1100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>9900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-10800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>4900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>200</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>3200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>100</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1449,7 +1472,7 @@
         <v>800</v>
       </c>
       <c r="L15" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="M15" s="3">
         <v>1100</v>
@@ -1467,13 +1490,13 @@
         <v>1100</v>
       </c>
       <c r="R15" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="S15" s="3">
         <v>1200</v>
       </c>
       <c r="T15" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="U15" s="3">
         <v>1500</v>
@@ -1503,13 +1526,13 @@
         <v>1500</v>
       </c>
       <c r="AD15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AE15" s="3">
         <v>1300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1700</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>400</v>
       </c>
       <c r="AG15" s="3">
         <v>400</v>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E17" s="3">
         <v>30100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>32300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>37100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>38200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>40400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>41700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>38300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>38500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>26100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>38000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>38500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>33800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>32700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>40600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>16000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>37000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>37700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>39200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>41900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>37000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>38500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>38900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>39700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>39800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>43800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>46100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>49500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>21200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>20500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1100</v>
-      </c>
-      <c r="H18" s="3">
-        <v>700</v>
       </c>
       <c r="I18" s="3">
         <v>700</v>
       </c>
       <c r="J18" s="3">
+        <v>700</v>
+      </c>
+      <c r="K18" s="3">
         <v>-200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>16700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-800</v>
       </c>
-      <c r="Y18" s="3">
-        <v>0</v>
-      </c>
       <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3">
         <v>1000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>300</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>500</v>
       </c>
       <c r="AH18" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1791,10 +1825,10 @@
         <v>100</v>
       </c>
       <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
-      </c>
-      <c r="F20" s="3">
-        <v>100</v>
       </c>
       <c r="G20" s="3">
         <v>100</v>
@@ -1806,7 +1840,7 @@
         <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1878,108 +1912,114 @@
         <v>0</v>
       </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2100</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1600</v>
       </c>
       <c r="I21" s="3">
         <v>1600</v>
       </c>
       <c r="J21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K21" s="3">
         <v>600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>17800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-8400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2017,25 +2057,25 @@
         <v>100</v>
       </c>
       <c r="O22" s="3">
+        <v>100</v>
+      </c>
+      <c r="P22" s="3">
         <v>500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3100</v>
-      </c>
-      <c r="U22" s="3">
-        <v>3200</v>
       </c>
       <c r="V22" s="3">
         <v>3200</v>
@@ -2044,236 +2084,245 @@
         <v>3200</v>
       </c>
       <c r="X22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="Y22" s="3">
         <v>3100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>3100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>3300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2400</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>400</v>
       </c>
       <c r="AG22" s="3">
         <v>400</v>
       </c>
       <c r="AH22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1100</v>
-      </c>
-      <c r="H23" s="3">
-        <v>700</v>
       </c>
       <c r="I23" s="3">
         <v>700</v>
       </c>
       <c r="J23" s="3">
+        <v>700</v>
+      </c>
+      <c r="K23" s="3">
         <v>-300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>16600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-12200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-900</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-6800</v>
-      </c>
-      <c r="H24" s="3">
-        <v>100</v>
       </c>
       <c r="I24" s="3">
         <v>100</v>
       </c>
       <c r="J24" s="3">
+        <v>100</v>
+      </c>
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>-100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-6400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>200</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>100</v>
       </c>
       <c r="AG24" s="3">
         <v>100</v>
       </c>
       <c r="AH24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7900</v>
-      </c>
-      <c r="H26" s="3">
-        <v>700</v>
       </c>
       <c r="I26" s="3">
         <v>700</v>
       </c>
       <c r="J26" s="3">
+        <v>700</v>
+      </c>
+      <c r="K26" s="3">
         <v>-800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-12600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>7200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5400</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-3600</v>
       </c>
       <c r="V26" s="3">
         <v>-3600</v>
       </c>
       <c r="W26" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="X26" s="3">
         <v>-6800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7900</v>
-      </c>
-      <c r="H27" s="3">
-        <v>700</v>
       </c>
       <c r="I27" s="3">
         <v>700</v>
       </c>
       <c r="J27" s="3">
+        <v>700</v>
+      </c>
+      <c r="K27" s="3">
         <v>-800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-12600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>31700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5400</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-3600</v>
       </c>
       <c r="V27" s="3">
         <v>-3600</v>
       </c>
       <c r="W27" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="X27" s="3">
         <v>-6800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2717,8 +2778,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2735,20 +2796,20 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>400</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>400</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2967,10 +3037,10 @@
         <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-100</v>
       </c>
       <c r="G32" s="3">
         <v>-100</v>
@@ -2982,7 +3052,7 @@
         <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3054,108 +3124,114 @@
         <v>0</v>
       </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7900</v>
-      </c>
-      <c r="H33" s="3">
-        <v>700</v>
       </c>
       <c r="I33" s="3">
         <v>700</v>
       </c>
       <c r="J33" s="3">
+        <v>700</v>
+      </c>
+      <c r="K33" s="3">
         <v>-800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-12600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>31700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5400</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-3600</v>
       </c>
       <c r="V33" s="3">
         <v>-3600</v>
       </c>
       <c r="W33" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="X33" s="3">
         <v>-6800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7900</v>
-      </c>
-      <c r="H35" s="3">
-        <v>700</v>
       </c>
       <c r="I35" s="3">
         <v>700</v>
       </c>
       <c r="J35" s="3">
+        <v>700</v>
+      </c>
+      <c r="K35" s="3">
         <v>-800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-12600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>31700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5400</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-3600</v>
       </c>
       <c r="V35" s="3">
         <v>-3600</v>
       </c>
       <c r="W35" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="X35" s="3">
         <v>-6800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E41" s="3">
         <v>21200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>18800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14300</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>14100</v>
       </c>
       <c r="R41" s="3">
         <v>14100</v>
       </c>
       <c r="S41" s="3">
+        <v>14100</v>
+      </c>
+      <c r="T41" s="3">
         <v>16600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,34 +3811,37 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E43" s="3">
         <v>14200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>18500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>19900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>20400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>20300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>22800</v>
-      </c>
-      <c r="K43" s="3">
-        <v>21200</v>
       </c>
       <c r="L43" s="3">
         <v>21200</v>
@@ -3757,70 +3850,73 @@
         <v>21200</v>
       </c>
       <c r="N43" s="3">
+        <v>21200</v>
+      </c>
+      <c r="O43" s="3">
         <v>23100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>20300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>19000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>18600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>16000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>17300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>20200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>20800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>20400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>20000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>19000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>20800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>21200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>20600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>22700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>23200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>24000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>13100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>12600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,204 +4013,213 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E45" s="3">
         <v>1400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>800</v>
       </c>
       <c r="L45" s="3">
         <v>800</v>
       </c>
       <c r="M45" s="3">
+        <v>800</v>
+      </c>
+      <c r="N45" s="3">
         <v>900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>900</v>
-      </c>
-      <c r="R45" s="3">
-        <v>1400</v>
       </c>
       <c r="S45" s="3">
         <v>1400</v>
       </c>
       <c r="T45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="U45" s="3">
         <v>1600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E46" s="3">
         <v>36800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>37000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>41800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>41400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>41300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>39500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>42200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>39500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>36200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>34200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>33700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>28500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>34700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>33600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>31500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>31700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>21200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>23700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>27100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>27400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>25100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>25000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>26200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>25700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>25300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>27500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>29000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>29400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>16200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>16400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>15600</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4211,70 +4316,73 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E48" s="3">
         <v>3800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4600</v>
-      </c>
-      <c r="M48" s="3">
-        <v>4700</v>
       </c>
       <c r="N48" s="3">
         <v>4700</v>
       </c>
       <c r="O48" s="3">
+        <v>4700</v>
+      </c>
+      <c r="P48" s="3">
         <v>4400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5100</v>
-      </c>
-      <c r="R48" s="3">
-        <v>5500</v>
       </c>
       <c r="S48" s="3">
         <v>5500</v>
       </c>
       <c r="T48" s="3">
-        <v>6300</v>
+        <v>5500</v>
       </c>
       <c r="U48" s="3">
         <v>6300</v>
       </c>
       <c r="V48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="W48" s="3">
         <v>900</v>
-      </c>
-      <c r="W48" s="3">
-        <v>800</v>
       </c>
       <c r="X48" s="3">
         <v>800</v>
@@ -4283,7 +4391,7 @@
         <v>800</v>
       </c>
       <c r="Z48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AA48" s="3">
         <v>900</v>
@@ -4301,114 +4409,120 @@
         <v>900</v>
       </c>
       <c r="AF48" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AG48" s="3">
         <v>500</v>
       </c>
       <c r="AH48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI48" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E49" s="3">
         <v>68300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>69000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>69700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>70400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>71100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>71900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>72600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>73300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>74000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>75000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>78200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>79200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>80200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>81200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>82300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>92300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>93400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>94800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>96200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>97600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>103300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>104700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>106100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>107500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>108900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>110200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>111600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>110300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>28900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>29300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,31 +4720,34 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E52" s="3">
         <v>8200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7000</v>
-      </c>
-      <c r="H52" s="3">
-        <v>700</v>
       </c>
       <c r="I52" s="3">
         <v>700</v>
       </c>
       <c r="J52" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="K52" s="3">
         <v>800</v>
@@ -4636,40 +4756,40 @@
         <v>800</v>
       </c>
       <c r="M52" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="N52" s="3">
         <v>1000</v>
       </c>
       <c r="O52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P52" s="3">
         <v>1100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>700</v>
-      </c>
-      <c r="S52" s="3">
-        <v>300</v>
       </c>
       <c r="T52" s="3">
         <v>300</v>
       </c>
       <c r="U52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="V52" s="3">
         <v>400</v>
       </c>
       <c r="W52" s="3">
+        <v>400</v>
+      </c>
+      <c r="X52" s="3">
         <v>600</v>
-      </c>
-      <c r="X52" s="3">
-        <v>400</v>
       </c>
       <c r="Y52" s="3">
         <v>400</v>
@@ -4681,10 +4801,10 @@
         <v>400</v>
       </c>
       <c r="AB52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AC52" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AD52" s="3">
         <v>300</v>
@@ -4693,7 +4813,7 @@
         <v>300</v>
       </c>
       <c r="AF52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AG52" s="3">
         <v>0</v>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>96900</v>
+      </c>
+      <c r="E54" s="3">
         <v>117000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>117600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>123600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>123700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>118100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>116200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>119600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>117800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>115600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>114900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>117600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>113300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>120200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>120500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>120000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>129800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>121200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>125200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>124500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>126300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>129600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>130900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>133600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>134400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>135100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>139000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>141800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>141000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>45700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>46300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>45900</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,106 +5099,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="E57" s="3">
         <v>2500</v>
       </c>
       <c r="F57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G57" s="3">
         <v>2800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2500</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>2000</v>
       </c>
       <c r="AB57" s="3">
         <v>2000</v>
       </c>
       <c r="AC57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AD57" s="3">
         <v>2100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5082,17 +5216,17 @@
         <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3" t="s">
+      <c r="I58" s="3">
+        <v>200</v>
+      </c>
+      <c r="J58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -5103,274 +5237,283 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>16700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>7900</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>1200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>17200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>16800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>15000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>12600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>14000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>8500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>10100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E59" s="3">
         <v>6700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>13800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>12500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>5000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E60" s="3">
         <v>9400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>23400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>26000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>22100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>18200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>24800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>18600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>15900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>14000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>13500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>13100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>27800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>26300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>26900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>19500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>27900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>14800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>16400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>200</v>
@@ -5379,11 +5522,11 @@
         <v>200</v>
       </c>
       <c r="H61" s="3">
+        <v>200</v>
+      </c>
+      <c r="I61" s="3">
         <v>300</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -5400,129 +5543,132 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>7000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>62500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>65000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>67400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>60700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>74900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>72500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>68200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>69800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>69900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>68800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>69900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>55000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>56000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>58500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>67600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>59000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>4800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="E62" s="3">
         <v>2200</v>
       </c>
       <c r="F62" s="3">
-        <v>3000</v>
+        <v>2200</v>
       </c>
       <c r="G62" s="3">
         <v>3000</v>
       </c>
       <c r="H62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I62" s="3">
         <v>3700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4600</v>
-      </c>
-      <c r="T62" s="3">
-        <v>4900</v>
       </c>
       <c r="U62" s="3">
         <v>4900</v>
       </c>
       <c r="V62" s="3">
+        <v>4900</v>
+      </c>
+      <c r="W62" s="3">
         <v>900</v>
-      </c>
-      <c r="W62" s="3">
-        <v>1200</v>
       </c>
       <c r="X62" s="3">
         <v>1200</v>
@@ -5531,25 +5677,25 @@
         <v>1200</v>
       </c>
       <c r="Z62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AA62" s="3">
         <v>700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4700</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>200</v>
       </c>
       <c r="AG62" s="3">
         <v>200</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E66" s="3">
         <v>11500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>18600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>17300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>36800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>35600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>94300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>93100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>92600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>90100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>91500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>90900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>87700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>86900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>85100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>83500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>83700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>84500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>84100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>86500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>88400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>91600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>21500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6235,13 +6403,13 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
-        <v>27700</v>
+        <v>0</v>
       </c>
       <c r="U70" s="3">
         <v>27700</v>
       </c>
       <c r="V70" s="3">
-        <v>27600</v>
+        <v>27700</v>
       </c>
       <c r="W70" s="3">
         <v>27600</v>
@@ -6253,7 +6421,7 @@
         <v>27600</v>
       </c>
       <c r="Z70" s="3">
-        <v>28800</v>
+        <v>27600</v>
       </c>
       <c r="AA70" s="3">
         <v>28800</v>
@@ -6262,7 +6430,7 @@
         <v>28800</v>
       </c>
       <c r="AC70" s="3">
-        <v>29300</v>
+        <v>28800</v>
       </c>
       <c r="AD70" s="3">
         <v>29300</v>
@@ -6271,7 +6439,7 @@
         <v>29300</v>
       </c>
       <c r="AF70" s="3">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="AG70" s="3">
         <v>0</v>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-4200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-9700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-10400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-11000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-10300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-12900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-14000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-30600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-33600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-32700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-31000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-30700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-18100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-49800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-44300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-40800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-37200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-30400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-26500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-23000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-22000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-20100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-17200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-15500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-19200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-13200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-13000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>86300</v>
+      </c>
+      <c r="E76" s="3">
         <v>105500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>106300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>109300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>110400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>102800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>102000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>101000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>101600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>98800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>97600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>80800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>77600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>25900</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>27400</v>
       </c>
       <c r="R76" s="3">
         <v>27400</v>
       </c>
       <c r="S76" s="3">
+        <v>27400</v>
+      </c>
+      <c r="T76" s="3">
         <v>39700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>19900</v>
-      </c>
-      <c r="Z76" s="3">
-        <v>21100</v>
       </c>
       <c r="AA76" s="3">
         <v>21100</v>
       </c>
       <c r="AB76" s="3">
+        <v>21100</v>
+      </c>
+      <c r="AC76" s="3">
         <v>22200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>23200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>24100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>20100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>25800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>24800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7900</v>
-      </c>
-      <c r="H81" s="3">
-        <v>700</v>
       </c>
       <c r="I81" s="3">
         <v>700</v>
       </c>
       <c r="J81" s="3">
+        <v>700</v>
+      </c>
+      <c r="K81" s="3">
         <v>-800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-12600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>31700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5400</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-3600</v>
       </c>
       <c r="V81" s="3">
         <v>-3600</v>
       </c>
       <c r="W81" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="X81" s="3">
         <v>-6800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7232,7 +7431,7 @@
         <v>800</v>
       </c>
       <c r="L83" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="M83" s="3">
         <v>1100</v>
@@ -7250,13 +7449,13 @@
         <v>1100</v>
       </c>
       <c r="R83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="S83" s="3">
         <v>1200</v>
       </c>
       <c r="T83" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="U83" s="3">
         <v>1500</v>
@@ -7286,13 +7485,13 @@
         <v>1500</v>
       </c>
       <c r="AD83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AE83" s="3">
         <v>1300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1700</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>400</v>
       </c>
       <c r="AG83" s="3">
         <v>400</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E89" s="3">
         <v>1300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>100</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>-2500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>800</v>
       </c>
       <c r="Z89" s="3">
         <v>800</v>
       </c>
       <c r="AA89" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB89" s="3">
         <v>500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7945,7 +8166,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
@@ -7966,7 +8187,7 @@
         <v>-100</v>
       </c>
       <c r="P91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -7981,13 +8202,13 @@
         <v>0</v>
       </c>
       <c r="U91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V91" s="3">
         <v>-100</v>
       </c>
       <c r="W91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -7996,23 +8217,23 @@
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC91" s="3">
         <v>-100</v>
       </c>
       <c r="AD91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
       <c r="AF91" s="3">
         <v>0</v>
       </c>
@@ -8020,10 +8241,13 @@
         <v>0</v>
       </c>
       <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,8 +8445,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8239,7 +8469,7 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3">
         <v>-100</v>
@@ -8260,7 +8490,7 @@
         <v>-100</v>
       </c>
       <c r="P94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -8275,13 +8505,13 @@
         <v>0</v>
       </c>
       <c r="U94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V94" s="3">
         <v>-100</v>
       </c>
       <c r="W94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -8290,34 +8520,37 @@
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC94" s="3">
         <v>-100</v>
       </c>
       <c r="AD94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-24800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-500</v>
-      </c>
-      <c r="AG94" s="3">
-        <v>-100</v>
       </c>
       <c r="AH94" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8753,20 +8999,20 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
-        <v>-1600</v>
+        <v>0</v>
       </c>
       <c r="F100" s="3">
         <v>-1600</v>
       </c>
       <c r="G100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="H100" s="3">
         <v>-500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
@@ -8783,11 +9029,11 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-4400</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
@@ -8795,55 +9041,58 @@
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>11900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>26700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E102" s="3">
         <v>1300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>100</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>-2500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>14200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
   <si>
     <t>JOB</t>
   </si>
@@ -1022,10 +1022,10 @@
         <v>13700</v>
       </c>
       <c r="I10" s="3">
-        <v>13300</v>
+        <v>13200</v>
       </c>
       <c r="J10" s="3">
-        <v>14300</v>
+        <v>14400</v>
       </c>
       <c r="K10" s="3">
         <v>15100</v>
@@ -1353,7 +1353,7 @@
         <v>500</v>
       </c>
       <c r="F14" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G14" s="3">
         <v>700</v>
@@ -1583,25 +1583,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>51400</v>
+        <v>30800</v>
       </c>
       <c r="E17" s="3">
-        <v>30100</v>
+        <v>29600</v>
       </c>
       <c r="F17" s="3">
-        <v>32300</v>
+        <v>31500</v>
       </c>
       <c r="G17" s="3">
-        <v>34800</v>
+        <v>34100</v>
       </c>
       <c r="H17" s="3">
         <v>37100</v>
       </c>
       <c r="I17" s="3">
-        <v>38200</v>
+        <v>38100</v>
       </c>
       <c r="J17" s="3">
-        <v>40400</v>
+        <v>40300</v>
       </c>
       <c r="K17" s="3">
         <v>41700</v>
@@ -1684,25 +1684,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-21900</v>
+        <v>-1400</v>
       </c>
       <c r="E18" s="3">
-        <v>-2000</v>
+        <v>-1600</v>
       </c>
       <c r="F18" s="3">
-        <v>-1700</v>
+        <v>-800</v>
       </c>
       <c r="G18" s="3">
-        <v>-500</v>
+        <v>200</v>
       </c>
       <c r="H18" s="3">
         <v>1100</v>
       </c>
       <c r="I18" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="J18" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K18" s="3">
         <v>-200</v>
@@ -1821,26 +1821,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>100</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1923,19 +1923,19 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-20900</v>
+        <v>-600</v>
       </c>
       <c r="E21" s="3">
-        <v>-1100</v>
+        <v>-800</v>
       </c>
       <c r="F21" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H21" s="3">
-        <v>2100</v>
+        <v>1900</v>
       </c>
       <c r="I21" s="3">
         <v>1600</v>
@@ -2231,8 +2231,8 @@
       <c r="E24" s="3">
         <v>-900</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G24" s="3">
         <v>-600</v>
@@ -3033,26 +3033,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-100</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3829,7 +3829,7 @@
         <v>15900</v>
       </c>
       <c r="G43" s="3">
-        <v>18500</v>
+        <v>18300</v>
       </c>
       <c r="H43" s="3">
         <v>19900</v>
@@ -3920,26 +3920,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4022,25 +4022,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>800</v>
-      </c>
-      <c r="H45" s="3">
-        <v>700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>800</v>
-      </c>
-      <c r="J45" s="3">
-        <v>700</v>
+        <v>200</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
         <v>600</v>
@@ -4132,7 +4132,7 @@
         <v>37000</v>
       </c>
       <c r="G46" s="3">
-        <v>41800</v>
+        <v>41700</v>
       </c>
       <c r="H46" s="3">
         <v>41400</v>
@@ -4223,26 +4223,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4729,19 +4729,19 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10900</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
-        <v>8200</v>
+        <v>400</v>
       </c>
       <c r="F52" s="3">
-        <v>7500</v>
+        <v>500</v>
       </c>
       <c r="G52" s="3">
-        <v>7700</v>
+        <v>600</v>
       </c>
       <c r="H52" s="3">
-        <v>7000</v>
+        <v>600</v>
       </c>
       <c r="I52" s="3">
         <v>700</v>
@@ -4940,7 +4940,7 @@
         <v>117600</v>
       </c>
       <c r="G54" s="3">
-        <v>123600</v>
+        <v>123500</v>
       </c>
       <c r="H54" s="3">
         <v>123700</v>
@@ -5207,25 +5207,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>1300</v>
       </c>
       <c r="E58" s="3">
-        <v>100</v>
+        <v>1400</v>
       </c>
       <c r="F58" s="3">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="G58" s="3">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="H58" s="3">
-        <v>200</v>
+        <v>1700</v>
       </c>
       <c r="I58" s="3">
-        <v>200</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
+        <v>1600</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1300</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5308,25 +5308,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6100</v>
+        <v>1000</v>
       </c>
       <c r="E59" s="3">
-        <v>6700</v>
+        <v>1100</v>
       </c>
       <c r="F59" s="3">
-        <v>6300</v>
+        <v>1600</v>
       </c>
       <c r="G59" s="3">
-        <v>10200</v>
+        <v>1500</v>
       </c>
       <c r="H59" s="3">
-        <v>7100</v>
+        <v>600</v>
       </c>
       <c r="I59" s="3">
-        <v>7800</v>
+        <v>800</v>
       </c>
       <c r="J59" s="3">
-        <v>8100</v>
+        <v>2000</v>
       </c>
       <c r="K59" s="3">
         <v>12600</v>
@@ -5418,7 +5418,7 @@
         <v>8900</v>
       </c>
       <c r="G60" s="3">
-        <v>11500</v>
+        <v>11400</v>
       </c>
       <c r="H60" s="3">
         <v>10100</v>
@@ -5510,25 +5510,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="F61" s="3">
-        <v>200</v>
+        <v>2400</v>
       </c>
       <c r="G61" s="3">
-        <v>200</v>
+        <v>2700</v>
       </c>
       <c r="H61" s="3">
-        <v>200</v>
+        <v>3100</v>
       </c>
       <c r="I61" s="3">
-        <v>300</v>
+        <v>3100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5610,26 +5610,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>1900</v>
-      </c>
-      <c r="E62" s="3">
-        <v>2200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>2200</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G62" s="3">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="H62" s="3">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="I62" s="3">
-        <v>3700</v>
+        <v>200</v>
       </c>
       <c r="J62" s="3">
-        <v>3100</v>
+        <v>500</v>
       </c>
       <c r="K62" s="3">
         <v>3000</v>
@@ -6024,7 +6024,7 @@
         <v>11300</v>
       </c>
       <c r="G66" s="3">
-        <v>14300</v>
+        <v>14200</v>
       </c>
       <c r="H66" s="3">
         <v>13300</v>
@@ -7407,25 +7407,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="E83" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>800</v>
@@ -8591,26 +8591,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -9096,26 +9096,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
   <si>
     <t>JOB</t>
   </si>
@@ -656,454 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>28300</v>
+      </c>
+      <c r="F8" s="3">
         <v>29500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>28100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>30600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>34300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>38200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>38900</v>
-      </c>
-      <c r="J8" s="3">
-        <v>41100</v>
-      </c>
-      <c r="K8" s="3">
-        <v>41500</v>
       </c>
       <c r="L8" s="3">
         <v>41100</v>
       </c>
       <c r="M8" s="3">
+        <v>41500</v>
+      </c>
+      <c r="N8" s="3">
+        <v>41100</v>
+      </c>
+      <c r="O8" s="3">
         <v>39600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>42800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>41500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>38100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>34700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>34600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>31000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>26600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>34700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>37600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>38900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>38100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>36200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>38500</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>39900</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>40300</v>
       </c>
       <c r="AC8" s="3">
         <v>39900</v>
       </c>
       <c r="AD8" s="3">
+        <v>40300</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>39900</v>
+      </c>
+      <c r="AF8" s="3">
         <v>45200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>46400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>46100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>21500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>21000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>18800</v>
+      </c>
+      <c r="F9" s="3">
         <v>19900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>19300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>20900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>22700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>24500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>25600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>26800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>26400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>24600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>25100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>27300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>26200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>24200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>23800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>22100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>20500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>16900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>22800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>25000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>25600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>24500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>24500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>25800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>25100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>25500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>26200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>29500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>29500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>29000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>15900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>15600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F10" s="3">
         <v>9600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>8800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>9700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>11600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>13700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>13200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>14400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>15100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>16500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>14500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>15500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>15300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>13900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>10900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>12500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>10500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>9700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>11900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>12600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>13300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>13600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>11700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>12700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>14800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>14800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>13700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>15700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>16900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>17100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>5600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>5400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1164,10 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1267,14 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,117 +1374,129 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>100</v>
+      </c>
+      <c r="F14" s="3">
         <v>20500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="F14" s="3">
-        <v>800</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
+        <v>500</v>
+      </c>
+      <c r="I14" s="3">
         <v>700</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>2000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-14100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-1100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>2200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>-200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>9900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-10800</v>
-      </c>
-      <c r="U14" s="3">
-        <v>1300</v>
-      </c>
-      <c r="V14" s="3">
-        <v>400</v>
       </c>
       <c r="W14" s="3">
         <v>1300</v>
       </c>
       <c r="X14" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Z14" s="3">
         <v>4900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>1200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>200</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>3200</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>100</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>0</v>
       </c>
       <c r="AI14" s="3">
         <v>100</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
         <v>800</v>
@@ -1475,10 +1520,10 @@
         <v>800</v>
       </c>
       <c r="M15" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="N15" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="O15" s="3">
         <v>1100</v>
@@ -1493,16 +1538,16 @@
         <v>1100</v>
       </c>
       <c r="S15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U15" s="3">
         <v>1200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>1200</v>
-      </c>
-      <c r="U15" s="3">
-        <v>1500</v>
-      </c>
-      <c r="V15" s="3">
-        <v>1500</v>
       </c>
       <c r="W15" s="3">
         <v>1500</v>
@@ -1529,22 +1574,28 @@
         <v>1500</v>
       </c>
       <c r="AE15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AG15" s="3">
         <v>1300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>1700</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>400</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>400</v>
       </c>
       <c r="AI15" s="3">
         <v>400</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>400</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1628,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>29700</v>
+      </c>
+      <c r="F17" s="3">
         <v>30800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>29600</v>
       </c>
-      <c r="F17" s="3">
-        <v>31500</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>31800</v>
+      </c>
+      <c r="I17" s="3">
         <v>34100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>37100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>38100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>40300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>41700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>38300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>38500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>26100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>38000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>38500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>33800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>32700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>40600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>16000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>37000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>37700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>39200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>41900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>37000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>38500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>38900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>39700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>39800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>43800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>46100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>49500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>21200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>20500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G18" s="3">
         <v>-1600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K18" s="3">
+        <v>800</v>
+      </c>
+      <c r="L18" s="3">
+        <v>800</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="O18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P18" s="3">
+        <v>16700</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>3500</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="S18" s="3">
+        <v>900</v>
+      </c>
+      <c r="T18" s="3">
+        <v>1900</v>
+      </c>
+      <c r="U18" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="V18" s="3">
+        <v>10600</v>
+      </c>
+      <c r="W18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-800</v>
       </c>
-      <c r="G18" s="3">
-        <v>200</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>800</v>
-      </c>
-      <c r="J18" s="3">
-        <v>800</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L18" s="3">
-        <v>2800</v>
-      </c>
-      <c r="M18" s="3">
-        <v>1100</v>
-      </c>
-      <c r="N18" s="3">
-        <v>16700</v>
-      </c>
-      <c r="O18" s="3">
-        <v>3500</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-400</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>900</v>
-      </c>
-      <c r="R18" s="3">
-        <v>1900</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="T18" s="3">
-        <v>10600</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3">
         <v>1000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>1400</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>-3400</v>
       </c>
       <c r="AG18" s="3">
         <v>300</v>
       </c>
       <c r="AH18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,8 +1881,10 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1842,11 +1909,11 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1915,111 +1982,123 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I21" s="3">
         <v>1000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>1900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>3600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>17800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>4600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>2000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>3100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-8400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>11800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>2500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>2100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>1500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>3000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>1600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2060,37 +2139,37 @@
         <v>100</v>
       </c>
       <c r="P22" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>100</v>
+      </c>
+      <c r="R22" s="3">
         <v>500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>2500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>2700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>2600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>3300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>3100</v>
-      </c>
-      <c r="V22" s="3">
-        <v>3200</v>
-      </c>
-      <c r="W22" s="3">
-        <v>3200</v>
       </c>
       <c r="X22" s="3">
         <v>3200</v>
       </c>
       <c r="Y22" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="Z22" s="3">
-        <v>2900</v>
+        <v>3200</v>
       </c>
       <c r="AA22" s="3">
         <v>3100</v>
@@ -2099,230 +2178,248 @@
         <v>2900</v>
       </c>
       <c r="AC22" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AE22" s="3">
         <v>2200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>3300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>2900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>2400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-21800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>16600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>3400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-12200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>7300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-5400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-3400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-3600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3">
+        <v>900</v>
+      </c>
+      <c r="F24" s="3">
         <v>-2500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-900</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3">
         <v>-600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-6800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>100</v>
-      </c>
-      <c r="K24" s="3">
-        <v>500</v>
       </c>
       <c r="L24" s="3">
         <v>100</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-100</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-6400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2519,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-19300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>7900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>2600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>16700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>3000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-12600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>7200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-5400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-3600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-3600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>3700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-19300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>7900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>2600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>16700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>3000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-12600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>31700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-5400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-3600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-3600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>3700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2840,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2781,11 +2902,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2799,24 +2920,24 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>400</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>400</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2826,8 +2947,14 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +3054,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,8 +3161,14 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3054,11 +3193,11 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3127,111 +3266,123 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-19300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>7900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>2600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>16700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>3000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-12600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>31700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-5400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-3600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-3600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>3700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3482,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-19300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>7900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>2600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>16700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>3000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-12600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>31700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-5400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-3600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-3600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>3700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3744,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3783,117 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>20800</v>
+      </c>
+      <c r="F41" s="3">
         <v>19600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>21200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>19900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>22500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>20700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>20100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>18500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>18800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>17500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>14200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>12100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>9900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>7400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>14300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>14100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>14100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>16600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>2400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>4100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>4200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>3500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>3200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>2600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>2900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>3500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>2900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>1600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>2200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,109 +3993,121 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>13700</v>
+      </c>
+      <c r="F43" s="3">
         <v>14600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>14200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>15900</v>
       </c>
-      <c r="G43" s="3">
-        <v>18300</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>18500</v>
+      </c>
+      <c r="J43" s="3">
         <v>19900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>20400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>20300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>22800</v>
-      </c>
-      <c r="L43" s="3">
-        <v>21200</v>
-      </c>
-      <c r="M43" s="3">
-        <v>21200</v>
       </c>
       <c r="N43" s="3">
         <v>21200</v>
       </c>
       <c r="O43" s="3">
+        <v>21200</v>
+      </c>
+      <c r="P43" s="3">
+        <v>21200</v>
+      </c>
+      <c r="Q43" s="3">
         <v>23100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>20300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>19000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>18600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>16000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>13700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>17300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>20200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>20800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>20400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>20000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>19000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>20800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>21200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>20600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>22700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>23200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>24000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>13100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>12600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3941,11 +4132,11 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4016,20 +4207,26 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4042,184 +4239,196 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>800</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="R45" s="3">
-        <v>900</v>
       </c>
       <c r="S45" s="3">
         <v>1400</v>
       </c>
       <c r="T45" s="3">
+        <v>900</v>
+      </c>
+      <c r="U45" s="3">
         <v>1400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W45" s="3">
         <v>1600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>2200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>2800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>2400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>2500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>2300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>1400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>3000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>2500</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AH45" s="3">
-        <v>1600</v>
       </c>
       <c r="AI45" s="3">
         <v>1500</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AK45" s="3">
+        <v>1500</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>35400</v>
+      </c>
+      <c r="F46" s="3">
         <v>35500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>36800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>37000</v>
       </c>
-      <c r="G46" s="3">
-        <v>41700</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
+        <v>41800</v>
+      </c>
+      <c r="J46" s="3">
         <v>41400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>41300</v>
-      </c>
-      <c r="J46" s="3">
-        <v>39500</v>
-      </c>
-      <c r="K46" s="3">
-        <v>42200</v>
       </c>
       <c r="L46" s="3">
         <v>39500</v>
       </c>
       <c r="M46" s="3">
+        <v>42200</v>
+      </c>
+      <c r="N46" s="3">
+        <v>39500</v>
+      </c>
+      <c r="O46" s="3">
         <v>36200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>34200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>33700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>28500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>34700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>33600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>31500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>31700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>21200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>23700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>27100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>27400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>25100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>25000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>26200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>25700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>25300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>27500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>29000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>29400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>16200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>16400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>15600</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4244,11 +4453,11 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4319,8 +4528,14 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4331,73 +4546,73 @@
         <v>3800</v>
       </c>
       <c r="F48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="H48" s="3">
         <v>4100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>4500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>4900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>5000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>4000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>4700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>4400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>4900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>5100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>5500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>5500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>6300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>6300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>900</v>
-      </c>
-      <c r="X48" s="3">
-        <v>800</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>800</v>
       </c>
       <c r="Z48" s="3">
         <v>800</v>
       </c>
       <c r="AA48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AB48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AC48" s="3">
         <v>900</v>
@@ -4412,117 +4627,129 @@
         <v>900</v>
       </c>
       <c r="AG48" s="3">
+        <v>900</v>
+      </c>
+      <c r="AH48" s="3">
+        <v>900</v>
+      </c>
+      <c r="AI48" s="3">
         <v>500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>46600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>46800</v>
+      </c>
+      <c r="F49" s="3">
         <v>47000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>68300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>69000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>69700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>70400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>71100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>71900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>72600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>73300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>74000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>75000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>78200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>79200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>80200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>81200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>82300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>92300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>93400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>94800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>96200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>97600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>103300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>104700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>106100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>107500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>108900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>110200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>111600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>110300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>28900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>29300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4849,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,79 +4956,85 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E52" s="3">
         <v>400</v>
       </c>
       <c r="F52" s="3">
+        <v>300</v>
+      </c>
+      <c r="G52" s="3">
+        <v>400</v>
+      </c>
+      <c r="H52" s="3">
         <v>500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>700</v>
-      </c>
-      <c r="K52" s="3">
-        <v>800</v>
-      </c>
-      <c r="L52" s="3">
-        <v>800</v>
       </c>
       <c r="M52" s="3">
         <v>800</v>
       </c>
       <c r="N52" s="3">
+        <v>800</v>
+      </c>
+      <c r="O52" s="3">
+        <v>800</v>
+      </c>
+      <c r="P52" s="3">
         <v>1000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>400</v>
-      </c>
-      <c r="W52" s="3">
-        <v>400</v>
-      </c>
-      <c r="X52" s="3">
-        <v>600</v>
       </c>
       <c r="Y52" s="3">
         <v>400</v>
       </c>
       <c r="Z52" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AA52" s="3">
         <v>400</v>
@@ -4804,28 +5043,34 @@
         <v>400</v>
       </c>
       <c r="AC52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AD52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AE52" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AF52" s="3">
         <v>300</v>
       </c>
       <c r="AG52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AH52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5170,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>92800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>95900</v>
+      </c>
+      <c r="F54" s="3">
         <v>96900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>117000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>117600</v>
       </c>
-      <c r="G54" s="3">
-        <v>123500</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
+        <v>123600</v>
+      </c>
+      <c r="J54" s="3">
         <v>123700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>118100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>116200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>119600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>117800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>115600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>114900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>117600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>113300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>120200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>120500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>120000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>129800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>121200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>125200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>124500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>126300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>129600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>130900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>133600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>134400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>135100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>139000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>141800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>141000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>45700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>46300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>45900</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5320,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,139 +5359,147 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F57" s="3">
         <v>2400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2800</v>
-      </c>
-      <c r="H57" s="3">
-        <v>2900</v>
-      </c>
-      <c r="I57" s="3">
-        <v>3400</v>
       </c>
       <c r="J57" s="3">
         <v>2900</v>
       </c>
       <c r="K57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="M57" s="3">
         <v>3000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>2100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>2600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>2900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>3700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>9100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>3900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>2900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>2500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>2000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>2000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>2100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>3200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>1400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>1300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>1600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E58" s="3">
         <v>1300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G58" s="3">
         <v>1400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K58" s="3">
         <v>1600</v>
       </c>
-      <c r="H58" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1300</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5240,70 +5507,76 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>16700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>11000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>8800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>5600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>2200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>7900</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>1200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>5700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>3900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>2200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>3200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>2400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>17200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>16800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>15000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>12600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>14000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>8500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>10100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5311,231 +5584,243 @@
         <v>1000</v>
       </c>
       <c r="E59" s="3">
+        <v>800</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G59" s="3">
         <v>1100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1600</v>
       </c>
-      <c r="G59" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J59" s="3">
         <v>600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>12600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>10400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>11600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>11300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>12200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>10600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>15400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>14600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>13900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>14400</v>
-      </c>
-      <c r="U59" s="3">
-        <v>9200</v>
-      </c>
-      <c r="V59" s="3">
-        <v>9300</v>
       </c>
       <c r="W59" s="3">
         <v>9200</v>
       </c>
       <c r="X59" s="3">
+        <v>9300</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>9200</v>
+      </c>
+      <c r="Z59" s="3">
         <v>2900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>7900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>7400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>8200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>8600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>7400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>9800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>13800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>12500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>5000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>4800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F60" s="3">
         <v>8600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>9400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>8900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>11500</v>
+      </c>
+      <c r="J60" s="3">
+        <v>10100</v>
+      </c>
+      <c r="K60" s="3">
         <v>11400</v>
       </c>
-      <c r="H60" s="3">
-        <v>10100</v>
-      </c>
-      <c r="I60" s="3">
-        <v>11400</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>11000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>15600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>12900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>13300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>13600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>31200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>23400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>26000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>22100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>18200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>24800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>11700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>13400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>18600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>15900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>14000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>13500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>13100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>27800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>26300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>26900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>19500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>27900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>14800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>16400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F61" s="3">
         <v>1900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2400</v>
       </c>
-      <c r="G61" s="3">
-        <v>2700</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J61" s="3">
         <v>3100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>3100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5546,67 +5831,73 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>7000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>62500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>65000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>67400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>60700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>74900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>72500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>68200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>69800</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>69900</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>68800</v>
       </c>
       <c r="AA61" s="3">
         <v>69900</v>
       </c>
       <c r="AB61" s="3">
+        <v>68800</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>69900</v>
+      </c>
+      <c r="AD61" s="3">
         <v>55000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>56000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>58500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>67600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>59000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>4900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>4800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5619,95 +5910,101 @@
       <c r="F62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G62" s="3">
-        <v>100</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3">
+        <v>400</v>
+      </c>
+      <c r="J62" s="3">
         <v>200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>3000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>3200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>3500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>3700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>5700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>5200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>5800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>6000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>7100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>4600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>4900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>4900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>900</v>
-      </c>
-      <c r="X62" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>1200</v>
       </c>
       <c r="Z62" s="3">
         <v>1200</v>
       </c>
       <c r="AA62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC62" s="3">
         <v>700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>1100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>4700</v>
-      </c>
-      <c r="AG62" s="3">
-        <v>200</v>
-      </c>
-      <c r="AH62" s="3">
-        <v>200</v>
       </c>
       <c r="AI62" s="3">
         <v>200</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>200</v>
+      </c>
+      <c r="AK62" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +6104,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6211,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6318,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F66" s="3">
         <v>10500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>11500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>11300</v>
       </c>
-      <c r="G66" s="3">
-        <v>14200</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
+        <v>14300</v>
+      </c>
+      <c r="J66" s="3">
         <v>13300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>15300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>14100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>18600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>16200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>16800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>17300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>36800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>35600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>94300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>93100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>92600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>90100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>91500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>90900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>87700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>86900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>85100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>83500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>83700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>84500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>84100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>86500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>88400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>91600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>19800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>21500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6468,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6571,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6678,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6406,16 +6741,16 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>27700</v>
       </c>
-      <c r="V70" s="3">
+      <c r="X70" s="3">
         <v>27700</v>
-      </c>
-      <c r="W70" s="3">
-        <v>27600</v>
-      </c>
-      <c r="X70" s="3">
-        <v>27600</v>
       </c>
       <c r="Y70" s="3">
         <v>27600</v>
@@ -6424,34 +6759,40 @@
         <v>27600</v>
       </c>
       <c r="AA70" s="3">
-        <v>28800</v>
+        <v>27600</v>
       </c>
       <c r="AB70" s="3">
-        <v>28800</v>
+        <v>27600</v>
       </c>
       <c r="AC70" s="3">
         <v>28800</v>
       </c>
       <c r="AD70" s="3">
-        <v>29300</v>
+        <v>28800</v>
       </c>
       <c r="AE70" s="3">
-        <v>29300</v>
+        <v>28800</v>
       </c>
       <c r="AF70" s="3">
         <v>29300</v>
       </c>
       <c r="AG70" s="3">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="AH70" s="3">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6892,121 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-23500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-4200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-3200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-1600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-1900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-9700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-10400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-11000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-10300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-12900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-14000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-30600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-33600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-32700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-31000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-30700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-18100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-49800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-44300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-40800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-37200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-30400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-26500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-23000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-22000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-20100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-17200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-15500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-19200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-13200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-13000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +7106,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7213,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7320,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>83600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>84200</v>
+      </c>
+      <c r="F76" s="3">
         <v>86300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>105500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>106300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>109300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>110400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>102800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>102000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>101000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>101600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>98800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>97600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>80800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>77600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>25900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>27400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>27400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>39700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>2000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>6600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>9200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>11900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>16900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>19900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>21100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>21100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>22200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>23200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>24100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>20100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>25800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>24800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7534,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-19300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>7900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>2600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>16700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>3000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-12600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>31700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-5400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-3600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-3600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>3700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,19 +7796,21 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>400</v>
+      </c>
+      <c r="F83" s="3">
         <v>1100</v>
-      </c>
-      <c r="E83" s="3">
-        <v>100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>100</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -7428,16 +7825,16 @@
         <v>100</v>
       </c>
       <c r="K83" s="3">
+        <v>100</v>
+      </c>
+      <c r="L83" s="3">
+        <v>100</v>
+      </c>
+      <c r="M83" s="3">
         <v>800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>800</v>
-      </c>
-      <c r="M83" s="3">
-        <v>1100</v>
-      </c>
-      <c r="N83" s="3">
-        <v>1100</v>
       </c>
       <c r="O83" s="3">
         <v>1100</v>
@@ -7452,16 +7849,16 @@
         <v>1100</v>
       </c>
       <c r="S83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U83" s="3">
         <v>1200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>1200</v>
-      </c>
-      <c r="U83" s="3">
-        <v>1500</v>
-      </c>
-      <c r="V83" s="3">
-        <v>1500</v>
       </c>
       <c r="W83" s="3">
         <v>1500</v>
@@ -7488,22 +7885,28 @@
         <v>1500</v>
       </c>
       <c r="AE83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AG83" s="3">
         <v>1300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>1700</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>400</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>400</v>
       </c>
       <c r="AI83" s="3">
         <v>400</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AK83" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +8006,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +8113,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8220,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8327,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8434,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-1500</v>
+        <v>-1100</v>
       </c>
       <c r="E89" s="3">
         <v>1300</v>
       </c>
       <c r="F89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="G89" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H89" s="3">
         <v>-900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>3300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>3500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>2300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>100</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>-2500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>2300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-1500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>1100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,8 +8584,10 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8169,10 +8610,10 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
@@ -8190,10 +8631,10 @@
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -8205,22 +8646,22 @@
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
       <c r="AA91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -8229,25 +8670,31 @@
         <v>-100</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-200</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
       <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8794,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,8 +8901,14 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8472,10 +8931,10 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L94" s="3">
         <v>-100</v>
@@ -8493,10 +8952,10 @@
         <v>-100</v>
       </c>
       <c r="Q94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -8508,22 +8967,22 @@
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
       <c r="AA94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB94" s="3">
         <v>0</v>
@@ -8532,25 +8991,31 @@
         <v>-100</v>
       </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-24800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +9051,10 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8612,11 +9079,11 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8687,8 +9154,14 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9261,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9368,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,8 +9475,14 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8999,26 +9490,26 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-1600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
@@ -9032,67 +9523,73 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>11900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>2200</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>-500</v>
       </c>
       <c r="AA100" s="3">
         <v>-100</v>
       </c>
       <c r="AB100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>-900</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>1100</v>
       </c>
       <c r="AE100" s="3">
         <v>-900</v>
       </c>
       <c r="AF100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AH100" s="3">
         <v>26700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9117,11 +9614,11 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9192,105 +9689,117 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>3400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>2000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>2200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>2600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>100</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>-2500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>14200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-1900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>1300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
   <si>
     <t>JOB</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E8" s="3">
         <v>26000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>29500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>28100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>30600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>34300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>38200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>38900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>41100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>41500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>41100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>39600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>42800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>41500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>38100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>31000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>26600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>34700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>37600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>38900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>38100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>36200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>38500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>39900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>40300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>39900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>45200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>46400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>46100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>21500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>21000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E9" s="3">
         <v>17700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>18800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>19900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>19300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>20900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>22700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>24500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>25600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>24600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>25100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>27300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>24200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>23800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>22100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>20500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>16900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>22800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>25000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>25600</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>24500</v>
       </c>
       <c r="AA9" s="3">
         <v>24500</v>
       </c>
       <c r="AB9" s="3">
+        <v>24500</v>
+      </c>
+      <c r="AC9" s="3">
         <v>25800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>25100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>25500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>26200</v>
-      </c>
-      <c r="AF9" s="3">
-        <v>29500</v>
       </c>
       <c r="AG9" s="3">
         <v>29500</v>
       </c>
       <c r="AH9" s="3">
+        <v>29500</v>
+      </c>
+      <c r="AI9" s="3">
         <v>29000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>15900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>15600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E10" s="3">
         <v>8300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>16500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>14500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>15500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>15300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>13900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>12500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>10500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>11900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>12600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>13300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>13600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>11700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>12700</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>14800</v>
       </c>
       <c r="AD10" s="3">
         <v>14800</v>
       </c>
       <c r="AE10" s="3">
+        <v>14800</v>
+      </c>
+      <c r="AF10" s="3">
         <v>13700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>15700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>16900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>17100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>5400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,115 +1397,121 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>100</v>
+        <v>22000</v>
       </c>
       <c r="E14" s="3">
         <v>100</v>
       </c>
       <c r="F14" s="3">
+        <v>100</v>
+      </c>
+      <c r="G14" s="3">
         <v>20500</v>
-      </c>
-      <c r="G14" s="3">
-        <v>500</v>
       </c>
       <c r="H14" s="3">
         <v>500</v>
       </c>
       <c r="I14" s="3">
+        <v>500</v>
+      </c>
+      <c r="J14" s="3">
         <v>700</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-1100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>9900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-10800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>4900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>200</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>3200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>100</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1499,7 +1522,7 @@
         <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="G15" s="3">
         <v>800</v>
@@ -1526,7 +1549,7 @@
         <v>800</v>
       </c>
       <c r="O15" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="P15" s="3">
         <v>1100</v>
@@ -1544,13 +1567,13 @@
         <v>1100</v>
       </c>
       <c r="U15" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="V15" s="3">
         <v>1200</v>
       </c>
       <c r="W15" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="X15" s="3">
         <v>1500</v>
@@ -1580,13 +1603,13 @@
         <v>1500</v>
       </c>
       <c r="AG15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AH15" s="3">
         <v>1300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>1700</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>400</v>
       </c>
       <c r="AJ15" s="3">
         <v>400</v>
@@ -1594,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>400</v>
       </c>
+      <c r="AL15" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E17" s="3">
         <v>26700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>30800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>29600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>31800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>34100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>37100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>38100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>40300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>41700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>38300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>38500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>26100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>38000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>38500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>33800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>32700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>40600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>16000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>37000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>37700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>39200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>41900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>37000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>38500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>38900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>39700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>39800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>43800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>46100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>49500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>21200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>20500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-700</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-1400</v>
       </c>
       <c r="F18" s="3">
         <v>-1400</v>
       </c>
       <c r="G18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="H18" s="3">
         <v>-1600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1100</v>
-      </c>
-      <c r="K18" s="3">
-        <v>800</v>
       </c>
       <c r="L18" s="3">
         <v>800</v>
       </c>
       <c r="M18" s="3">
+        <v>800</v>
+      </c>
+      <c r="N18" s="3">
         <v>-200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>16700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>10600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-800</v>
       </c>
-      <c r="AB18" s="3">
-        <v>0</v>
-      </c>
       <c r="AC18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="3">
         <v>1000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>300</v>
-      </c>
-      <c r="AJ18" s="3">
-        <v>500</v>
       </c>
       <c r="AK18" s="3">
         <v>500</v>
       </c>
+      <c r="AL18" s="3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1915,8 +1949,8 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1988,117 +2022,123 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1900</v>
-      </c>
-      <c r="K21" s="3">
-        <v>1600</v>
       </c>
       <c r="L21" s="3">
         <v>1600</v>
       </c>
       <c r="M21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N21" s="3">
         <v>600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>17800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-8400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>11800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2145,25 +2185,25 @@
         <v>100</v>
       </c>
       <c r="R22" s="3">
+        <v>100</v>
+      </c>
+      <c r="S22" s="3">
         <v>500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3100</v>
-      </c>
-      <c r="X22" s="3">
-        <v>3200</v>
       </c>
       <c r="Y22" s="3">
         <v>3200</v>
@@ -2172,254 +2212,263 @@
         <v>3200</v>
       </c>
       <c r="AA22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AB22" s="3">
         <v>3100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>3100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>2900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>2400</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>400</v>
       </c>
       <c r="AJ22" s="3">
         <v>400</v>
       </c>
       <c r="AK22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AL22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-21800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1100</v>
-      </c>
-      <c r="K23" s="3">
-        <v>700</v>
       </c>
       <c r="L23" s="3">
         <v>700</v>
       </c>
       <c r="M23" s="3">
+        <v>700</v>
+      </c>
+      <c r="N23" s="3">
         <v>-300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>16600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-12200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-900</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3">
         <v>-600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-6800</v>
-      </c>
-      <c r="K24" s="3">
-        <v>100</v>
       </c>
       <c r="L24" s="3">
         <v>100</v>
       </c>
       <c r="M24" s="3">
+        <v>100</v>
+      </c>
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-100</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-6400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>200</v>
-      </c>
-      <c r="AI24" s="3">
-        <v>100</v>
       </c>
       <c r="AJ24" s="3">
         <v>100</v>
       </c>
       <c r="AK24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7900</v>
-      </c>
-      <c r="K26" s="3">
-        <v>700</v>
       </c>
       <c r="L26" s="3">
         <v>700</v>
       </c>
       <c r="M26" s="3">
+        <v>700</v>
+      </c>
+      <c r="N26" s="3">
         <v>-800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>16700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-12600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>7200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5400</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-3600</v>
       </c>
       <c r="Y26" s="3">
         <v>-3600</v>
       </c>
       <c r="Z26" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7900</v>
-      </c>
-      <c r="K27" s="3">
-        <v>700</v>
       </c>
       <c r="L27" s="3">
         <v>700</v>
       </c>
       <c r="M27" s="3">
+        <v>700</v>
+      </c>
+      <c r="N27" s="3">
         <v>-800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>16700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-12600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>31700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5400</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-3600</v>
       </c>
       <c r="Y27" s="3">
         <v>-3600</v>
       </c>
       <c r="Z27" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,13 +2904,16 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2908,8 +2969,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2926,21 +2987,21 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>400</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>400</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3199,8 +3269,8 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -3272,117 +3342,123 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7900</v>
-      </c>
-      <c r="K33" s="3">
-        <v>700</v>
       </c>
       <c r="L33" s="3">
         <v>700</v>
       </c>
       <c r="M33" s="3">
+        <v>700</v>
+      </c>
+      <c r="N33" s="3">
         <v>-800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>16700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-12600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>31700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5400</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-3600</v>
       </c>
       <c r="Y33" s="3">
         <v>-3600</v>
       </c>
       <c r="Z33" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7900</v>
-      </c>
-      <c r="K35" s="3">
-        <v>700</v>
       </c>
       <c r="L35" s="3">
         <v>700</v>
       </c>
       <c r="M35" s="3">
+        <v>700</v>
+      </c>
+      <c r="N35" s="3">
         <v>-800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>16700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-12600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>31700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5400</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-3600</v>
       </c>
       <c r="Y35" s="3">
         <v>-3600</v>
       </c>
       <c r="Z35" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E41" s="3">
         <v>19700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>19600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>22500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>20100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>18800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>14300</v>
-      </c>
-      <c r="T41" s="3">
-        <v>14100</v>
       </c>
       <c r="U41" s="3">
         <v>14100</v>
       </c>
       <c r="V41" s="3">
+        <v>14100</v>
+      </c>
+      <c r="W41" s="3">
         <v>16600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3999,43 +4089,46 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E43" s="3">
         <v>12300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>14200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>18500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>19900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>22800</v>
-      </c>
-      <c r="N43" s="3">
-        <v>21200</v>
       </c>
       <c r="O43" s="3">
         <v>21200</v>
@@ -4044,70 +4137,73 @@
         <v>21200</v>
       </c>
       <c r="Q43" s="3">
+        <v>21200</v>
+      </c>
+      <c r="R43" s="3">
         <v>23100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>20300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>19000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>18600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>16000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>13700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>17300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>20200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>20800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>20400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>20000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>19000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>20800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>21200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>20600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>22700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>23200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>24000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>13100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>12600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4138,8 +4234,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4213,23 +4309,26 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>1200</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4245,190 +4344,196 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>600</v>
-      </c>
-      <c r="N45" s="3">
-        <v>800</v>
       </c>
       <c r="O45" s="3">
         <v>800</v>
       </c>
       <c r="P45" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>900</v>
-      </c>
-      <c r="U45" s="3">
-        <v>1400</v>
       </c>
       <c r="V45" s="3">
         <v>1400</v>
       </c>
       <c r="W45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="X45" s="3">
         <v>1600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E46" s="3">
         <v>33000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>35400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>35500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>36800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>37000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>41800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>41400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>41300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>39500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>42200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>39500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>34200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>33700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>28500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>34700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>33600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>31500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>31700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>21200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>23700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>27100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>27400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>25100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>25000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>26200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>25700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>25300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>27500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>29000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>29400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>16200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>16400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>15600</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4459,8 +4564,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4534,79 +4639,82 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E48" s="3">
         <v>3400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4600</v>
-      </c>
-      <c r="P48" s="3">
-        <v>4700</v>
       </c>
       <c r="Q48" s="3">
         <v>4700</v>
       </c>
       <c r="R48" s="3">
+        <v>4700</v>
+      </c>
+      <c r="S48" s="3">
         <v>4400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5100</v>
-      </c>
-      <c r="U48" s="3">
-        <v>5500</v>
       </c>
       <c r="V48" s="3">
         <v>5500</v>
       </c>
       <c r="W48" s="3">
-        <v>6300</v>
+        <v>5500</v>
       </c>
       <c r="X48" s="3">
         <v>6300</v>
       </c>
       <c r="Y48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="Z48" s="3">
         <v>900</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>800</v>
       </c>
       <c r="AA48" s="3">
         <v>800</v>
@@ -4615,7 +4723,7 @@
         <v>800</v>
       </c>
       <c r="AC48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AD48" s="3">
         <v>900</v>
@@ -4633,123 +4741,129 @@
         <v>900</v>
       </c>
       <c r="AI48" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AJ48" s="3">
         <v>500</v>
       </c>
       <c r="AK48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AL48" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E49" s="3">
         <v>46600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>46800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>47000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>68300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>69000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>69700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>70400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>71100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>71900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>72600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>73300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>74000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>75000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>78200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>79200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>80200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>81200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>82300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>92300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>93400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>94800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>96200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>97600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>103300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>104700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>106100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>107500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>108900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>110200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>111600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>110300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>28900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>29300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,8 +5079,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4971,31 +5091,31 @@
         <v>200</v>
       </c>
       <c r="E52" s="3">
+        <v>200</v>
+      </c>
+      <c r="F52" s="3">
         <v>400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>500</v>
-      </c>
-      <c r="I52" s="3">
-        <v>600</v>
       </c>
       <c r="J52" s="3">
         <v>600</v>
       </c>
       <c r="K52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="L52" s="3">
         <v>700</v>
       </c>
       <c r="M52" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="N52" s="3">
         <v>800</v>
@@ -5004,40 +5124,40 @@
         <v>800</v>
       </c>
       <c r="P52" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="Q52" s="3">
         <v>1000</v>
       </c>
       <c r="R52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S52" s="3">
         <v>1100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>700</v>
-      </c>
-      <c r="V52" s="3">
-        <v>300</v>
       </c>
       <c r="W52" s="3">
         <v>300</v>
       </c>
       <c r="X52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Y52" s="3">
         <v>400</v>
       </c>
       <c r="Z52" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA52" s="3">
         <v>600</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>400</v>
       </c>
       <c r="AB52" s="3">
         <v>400</v>
@@ -5049,10 +5169,10 @@
         <v>400</v>
       </c>
       <c r="AE52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AF52" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AG52" s="3">
         <v>300</v>
@@ -5061,7 +5181,7 @@
         <v>300</v>
       </c>
       <c r="AI52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AJ52" s="3">
         <v>0</v>
@@ -5069,8 +5189,11 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>61800</v>
+      </c>
+      <c r="E54" s="3">
         <v>92800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>95900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>96900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>117000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>117600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>123600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>123700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>118100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>116200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>119600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>117800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>115600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>114900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>117600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>113300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>120200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>120500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>120000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>129800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>121200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>125200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>124500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>126300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>129600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>130900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>133600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>134400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>135100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>139000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>141800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>141000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>45700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>46300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>45900</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,115 +5491,119 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2400</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2500</v>
       </c>
       <c r="H57" s="3">
         <v>2500</v>
       </c>
       <c r="I57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J57" s="3">
         <v>2800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2500</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>2000</v>
       </c>
       <c r="AE57" s="3">
         <v>2000</v>
       </c>
       <c r="AF57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AG57" s="3">
         <v>2100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5477,32 +5611,32 @@
         <v>1200</v>
       </c>
       <c r="E58" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F58" s="3">
         <v>1300</v>
       </c>
       <c r="G58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H58" s="3">
         <v>1400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1500</v>
       </c>
       <c r="I58" s="3">
         <v>1500</v>
       </c>
       <c r="J58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K58" s="3">
         <v>1700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1300</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5513,317 +5647,326 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>16700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>11000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>8800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7900</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>1200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>17200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>16800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>15000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>12600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>14000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>10100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>7900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>9800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>13800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>12500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E60" s="3">
         <v>7000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>31200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>23400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>26000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>22100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>18200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>24800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>13400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>18600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>15900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>14000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>13500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>13100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>27800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>26300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>26900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>19500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>27900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>14800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>16400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E61" s="3">
         <v>2100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2500</v>
-      </c>
-      <c r="J61" s="3">
-        <v>3100</v>
       </c>
       <c r="K61" s="3">
         <v>3100</v>
       </c>
       <c r="L61" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M61" s="3">
         <v>2000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5837,72 +5980,75 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>7000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>62500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>65000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>67400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>60700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>74900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>72500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>68200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>69800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>69900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>68800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>69900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>55000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>56000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>58500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>67600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>59000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>4900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>4800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>8</v>
+      <c r="D62" s="3">
+        <v>0</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>8</v>
@@ -5916,59 +6062,59 @@
       <c r="H62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3">
         <v>400</v>
-      </c>
-      <c r="J62" s="3">
-        <v>200</v>
       </c>
       <c r="K62" s="3">
         <v>200</v>
       </c>
       <c r="L62" s="3">
+        <v>200</v>
+      </c>
+      <c r="M62" s="3">
         <v>500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4600</v>
-      </c>
-      <c r="W62" s="3">
-        <v>4900</v>
       </c>
       <c r="X62" s="3">
         <v>4900</v>
       </c>
       <c r="Y62" s="3">
+        <v>4900</v>
+      </c>
+      <c r="Z62" s="3">
         <v>900</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>1200</v>
       </c>
       <c r="AA62" s="3">
         <v>1200</v>
@@ -5977,25 +6123,25 @@
         <v>1200</v>
       </c>
       <c r="AC62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AD62" s="3">
         <v>700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4700</v>
-      </c>
-      <c r="AI62" s="3">
-        <v>200</v>
       </c>
       <c r="AJ62" s="3">
         <v>200</v>
@@ -6003,8 +6149,11 @@
       <c r="AK62" s="3">
         <v>200</v>
       </c>
+      <c r="AL62" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E66" s="3">
         <v>9200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>17300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>36800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>35600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>94300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>93100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>92600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>90100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>91500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>90900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>87700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>86900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>85100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>83500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>83700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>84500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>84100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>86500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>88400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>91600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>19800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>21500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6747,13 +6915,13 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
-        <v>27700</v>
+        <v>0</v>
       </c>
       <c r="X70" s="3">
         <v>27700</v>
       </c>
       <c r="Y70" s="3">
-        <v>27600</v>
+        <v>27700</v>
       </c>
       <c r="Z70" s="3">
         <v>27600</v>
@@ -6765,7 +6933,7 @@
         <v>27600</v>
       </c>
       <c r="AC70" s="3">
-        <v>28800</v>
+        <v>27600</v>
       </c>
       <c r="AD70" s="3">
         <v>28800</v>
@@ -6774,7 +6942,7 @@
         <v>28800</v>
       </c>
       <c r="AF70" s="3">
-        <v>29300</v>
+        <v>28800</v>
       </c>
       <c r="AG70" s="3">
         <v>29300</v>
@@ -6783,7 +6951,7 @@
         <v>29300</v>
       </c>
       <c r="AI70" s="3">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="AJ70" s="3">
         <v>0</v>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-59500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-26400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-25700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-23500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-4200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-9700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-10400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-11000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-10300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-12900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-30600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-33600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-32700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-31000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-30700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-18100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-49800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-44300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-40800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-37200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-30400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-26500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-23000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-22000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-20100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-17200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-15500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-19200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-13200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-13000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E76" s="3">
         <v>83600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>84200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>86300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>105500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>106300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>109300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>110400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>102800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>102000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>101000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>101600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>98800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>97600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>80800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>77600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>25900</v>
-      </c>
-      <c r="T76" s="3">
-        <v>27400</v>
       </c>
       <c r="U76" s="3">
         <v>27400</v>
       </c>
       <c r="V76" s="3">
+        <v>27400</v>
+      </c>
+      <c r="W76" s="3">
         <v>39700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>16900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>19900</v>
-      </c>
-      <c r="AC76" s="3">
-        <v>21100</v>
       </c>
       <c r="AD76" s="3">
         <v>21100</v>
       </c>
       <c r="AE76" s="3">
+        <v>21100</v>
+      </c>
+      <c r="AF76" s="3">
         <v>22200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>23200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>24100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>20100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>25800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>24800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7900</v>
-      </c>
-      <c r="K81" s="3">
-        <v>700</v>
       </c>
       <c r="L81" s="3">
         <v>700</v>
       </c>
       <c r="M81" s="3">
+        <v>700</v>
+      </c>
+      <c r="N81" s="3">
         <v>-800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>16700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-12600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>31700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5400</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-3600</v>
       </c>
       <c r="Y81" s="3">
         <v>-3600</v>
       </c>
       <c r="Z81" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,22 +7996,23 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>400</v>
       </c>
       <c r="F83" s="3">
+        <v>400</v>
+      </c>
+      <c r="G83" s="3">
         <v>1100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -7831,13 +8030,13 @@
         <v>100</v>
       </c>
       <c r="M83" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>800</v>
       </c>
       <c r="O83" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="P83" s="3">
         <v>1100</v>
@@ -7855,13 +8054,13 @@
         <v>1100</v>
       </c>
       <c r="U83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="V83" s="3">
         <v>1200</v>
       </c>
       <c r="W83" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="X83" s="3">
         <v>1500</v>
@@ -7891,13 +8090,13 @@
         <v>1500</v>
       </c>
       <c r="AG83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AH83" s="3">
         <v>1300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1700</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>400</v>
       </c>
       <c r="AJ83" s="3">
         <v>400</v>
@@ -7905,8 +8104,11 @@
       <c r="AK83" s="3">
         <v>400</v>
       </c>
+      <c r="AL83" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>100</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>-2500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-600</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>800</v>
       </c>
       <c r="AC89" s="3">
         <v>800</v>
       </c>
       <c r="AD89" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE89" s="3">
         <v>500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,8 +8806,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8616,7 +8837,7 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
@@ -8637,7 +8858,7 @@
         <v>-100</v>
       </c>
       <c r="S91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -8652,13 +8873,13 @@
         <v>0</v>
       </c>
       <c r="X91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y91" s="3">
         <v>-100</v>
       </c>
       <c r="Z91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
@@ -8667,23 +8888,23 @@
         <v>0</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
       <c r="AE91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF91" s="3">
         <v>-100</v>
       </c>
       <c r="AG91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-200</v>
       </c>
-      <c r="AH91" s="3">
-        <v>0</v>
-      </c>
       <c r="AI91" s="3">
         <v>0</v>
       </c>
@@ -8691,10 +8912,13 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,13 +9134,16 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -8937,7 +9167,7 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M94" s="3">
         <v>-100</v>
@@ -8958,7 +9188,7 @@
         <v>-100</v>
       </c>
       <c r="S94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -8973,13 +9203,13 @@
         <v>0</v>
       </c>
       <c r="X94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y94" s="3">
         <v>-100</v>
       </c>
       <c r="Z94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -8988,34 +9218,37 @@
         <v>0</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
       <c r="AE94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF94" s="3">
         <v>-100</v>
       </c>
       <c r="AG94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-24800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-500</v>
-      </c>
-      <c r="AJ94" s="3">
-        <v>-100</v>
       </c>
       <c r="AK94" s="3">
         <v>-100</v>
       </c>
+      <c r="AL94" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9085,8 +9319,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,8 +9724,11 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9490,29 +9736,29 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>-1600</v>
+        <v>0</v>
       </c>
       <c r="I100" s="3">
         <v>-1600</v>
       </c>
       <c r="J100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="K100" s="3">
         <v>-500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
@@ -9529,11 +9775,11 @@
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-4400</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
@@ -9541,55 +9787,58 @@
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>11900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>26700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9620,8 +9869,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9695,111 +9944,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>100</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>-2500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>14200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>JOB</t>
   </si>
@@ -656,162 +656,166 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -819,329 +823,338 @@
         <v>24500</v>
       </c>
       <c r="E8" s="3">
-        <v>26000</v>
+        <v>24500</v>
       </c>
       <c r="F8" s="3">
+        <v>24000</v>
+      </c>
+      <c r="G8" s="3">
         <v>28300</v>
       </c>
-      <c r="G8" s="3">
-        <v>29500</v>
-      </c>
       <c r="H8" s="3">
+        <v>27000</v>
+      </c>
+      <c r="I8" s="3">
+        <v>25600</v>
+      </c>
+      <c r="J8" s="3">
         <v>28100</v>
       </c>
-      <c r="I8" s="3">
-        <v>30600</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>34300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>38200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>38900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>41100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>41500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>41100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>39600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>42800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>41500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>38100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>34600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>31000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>26600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>34700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>37600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>38900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>38100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>36200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>38500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>39900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>40300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>39900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>45200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>46400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>46100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>21500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>21000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E9" s="3">
         <v>16100</v>
       </c>
-      <c r="E9" s="3">
-        <v>17700</v>
-      </c>
       <c r="F9" s="3">
+        <v>16100</v>
+      </c>
+      <c r="G9" s="3">
         <v>18800</v>
       </c>
-      <c r="G9" s="3">
-        <v>19900</v>
-      </c>
       <c r="H9" s="3">
-        <v>19300</v>
+        <v>17800</v>
       </c>
       <c r="I9" s="3">
-        <v>20900</v>
+        <v>17200</v>
       </c>
       <c r="J9" s="3">
+        <v>18800</v>
+      </c>
+      <c r="K9" s="3">
         <v>22700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>24500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>25600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>24600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>25100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>27300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>24200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>23800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>22100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>20500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>16900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>22800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>25000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>25600</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>24500</v>
       </c>
       <c r="AB9" s="3">
         <v>24500</v>
       </c>
       <c r="AC9" s="3">
+        <v>24500</v>
+      </c>
+      <c r="AD9" s="3">
         <v>25800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>25100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>25500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>26200</v>
-      </c>
-      <c r="AG9" s="3">
-        <v>29500</v>
       </c>
       <c r="AH9" s="3">
         <v>29500</v>
       </c>
       <c r="AI9" s="3">
+        <v>29500</v>
+      </c>
+      <c r="AJ9" s="3">
         <v>29000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>15900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>15600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E10" s="3">
         <v>8400</v>
       </c>
-      <c r="E10" s="3">
-        <v>8300</v>
-      </c>
       <c r="F10" s="3">
+        <v>7900</v>
+      </c>
+      <c r="G10" s="3">
         <v>9500</v>
       </c>
-      <c r="G10" s="3">
-        <v>9600</v>
-      </c>
       <c r="H10" s="3">
-        <v>8800</v>
+        <v>9200</v>
       </c>
       <c r="I10" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>9300</v>
+      </c>
+      <c r="K10" s="3">
+        <v>11600</v>
+      </c>
+      <c r="L10" s="3">
+        <v>13700</v>
+      </c>
+      <c r="M10" s="3">
+        <v>13200</v>
+      </c>
+      <c r="N10" s="3">
+        <v>14400</v>
+      </c>
+      <c r="O10" s="3">
+        <v>15100</v>
+      </c>
+      <c r="P10" s="3">
+        <v>16500</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>14500</v>
+      </c>
+      <c r="R10" s="3">
+        <v>15500</v>
+      </c>
+      <c r="S10" s="3">
+        <v>15300</v>
+      </c>
+      <c r="T10" s="3">
+        <v>13900</v>
+      </c>
+      <c r="U10" s="3">
+        <v>10900</v>
+      </c>
+      <c r="V10" s="3">
+        <v>12500</v>
+      </c>
+      <c r="W10" s="3">
+        <v>10500</v>
+      </c>
+      <c r="X10" s="3">
         <v>9700</v>
       </c>
-      <c r="J10" s="3">
-        <v>11600</v>
-      </c>
-      <c r="K10" s="3">
-        <v>13700</v>
-      </c>
-      <c r="L10" s="3">
-        <v>13200</v>
-      </c>
-      <c r="M10" s="3">
-        <v>14400</v>
-      </c>
-      <c r="N10" s="3">
-        <v>15100</v>
-      </c>
-      <c r="O10" s="3">
-        <v>16500</v>
-      </c>
-      <c r="P10" s="3">
-        <v>14500</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>15500</v>
-      </c>
-      <c r="R10" s="3">
-        <v>15300</v>
-      </c>
-      <c r="S10" s="3">
-        <v>13900</v>
-      </c>
-      <c r="T10" s="3">
-        <v>10900</v>
-      </c>
-      <c r="U10" s="3">
-        <v>12500</v>
-      </c>
-      <c r="V10" s="3">
-        <v>10500</v>
-      </c>
-      <c r="W10" s="3">
-        <v>9700</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>11900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>12600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>13300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>13600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>11700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>12700</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>14800</v>
       </c>
       <c r="AE10" s="3">
         <v>14800</v>
       </c>
       <c r="AF10" s="3">
+        <v>14800</v>
+      </c>
+      <c r="AG10" s="3">
         <v>13700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>15700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>16900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>17100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>5600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>5400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,118 +1417,124 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>22000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
+        <v>19500</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
+        <v>700</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
-        <v>20500</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>200</v>
+      </c>
+      <c r="P14" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="R14" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="S14" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="T14" s="3">
+        <v>2200</v>
+      </c>
+      <c r="U14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V14" s="3">
+        <v>100</v>
+      </c>
+      <c r="W14" s="3">
+        <v>9900</v>
+      </c>
+      <c r="X14" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF14" s="3">
         <v>500</v>
       </c>
-      <c r="I14" s="3">
-        <v>500</v>
-      </c>
-      <c r="J14" s="3">
-        <v>700</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="AG14" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>600</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AK14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>200</v>
-      </c>
-      <c r="O14" s="3">
-        <v>300</v>
-      </c>
-      <c r="P14" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>-14100</v>
-      </c>
-      <c r="R14" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="S14" s="3">
-        <v>2200</v>
-      </c>
-      <c r="T14" s="3">
-        <v>-200</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>100</v>
       </c>
-      <c r="V14" s="3">
-        <v>9900</v>
-      </c>
-      <c r="W14" s="3">
-        <v>-10800</v>
-      </c>
-      <c r="X14" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>400</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>1300</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>4900</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>600</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>1200</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>800</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>500</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>200</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>600</v>
-      </c>
-      <c r="AI14" s="3">
-        <v>3200</v>
-      </c>
-      <c r="AJ14" s="3">
-        <v>100</v>
-      </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="3">
-        <v>100</v>
-      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1525,7 +1548,7 @@
         <v>300</v>
       </c>
       <c r="G15" s="3">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="H15" s="3">
         <v>800</v>
@@ -1552,7 +1575,7 @@
         <v>800</v>
       </c>
       <c r="P15" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="Q15" s="3">
         <v>1100</v>
@@ -1570,13 +1593,13 @@
         <v>1100</v>
       </c>
       <c r="V15" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="W15" s="3">
         <v>1200</v>
       </c>
       <c r="X15" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="Y15" s="3">
         <v>1500</v>
@@ -1606,13 +1629,13 @@
         <v>1500</v>
       </c>
       <c r="AH15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AI15" s="3">
         <v>1300</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>1700</v>
-      </c>
-      <c r="AJ15" s="3">
-        <v>400</v>
       </c>
       <c r="AK15" s="3">
         <v>400</v>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>400</v>
       </c>
+      <c r="AM15" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E17" s="3">
         <v>25700</v>
       </c>
-      <c r="E17" s="3">
-        <v>26700</v>
-      </c>
       <c r="F17" s="3">
+        <v>24800</v>
+      </c>
+      <c r="G17" s="3">
         <v>29700</v>
       </c>
-      <c r="G17" s="3">
-        <v>30800</v>
-      </c>
       <c r="H17" s="3">
-        <v>29600</v>
+        <v>28300</v>
       </c>
       <c r="I17" s="3">
-        <v>31800</v>
+        <v>27500</v>
       </c>
       <c r="J17" s="3">
+        <v>29800</v>
+      </c>
+      <c r="K17" s="3">
         <v>34100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>37100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>38100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>40300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>41700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>38300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>38500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>26100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>38000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>38500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>33800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>32700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>40600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>16000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>37000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>37700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>39200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>41900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>37000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>38500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>38900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>39700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>39800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>43800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>46100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>49500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>21200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>20500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1200</v>
       </c>
-      <c r="E18" s="3">
-        <v>-700</v>
-      </c>
       <c r="F18" s="3">
-        <v>-1400</v>
+        <v>-800</v>
       </c>
       <c r="G18" s="3">
         <v>-1400</v>
       </c>
       <c r="H18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1600</v>
       </c>
-      <c r="I18" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1100</v>
-      </c>
-      <c r="L18" s="3">
-        <v>800</v>
       </c>
       <c r="M18" s="3">
         <v>800</v>
       </c>
       <c r="N18" s="3">
+        <v>800</v>
+      </c>
+      <c r="O18" s="3">
         <v>-200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>16700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-9600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-800</v>
       </c>
-      <c r="AC18" s="3">
-        <v>0</v>
-      </c>
       <c r="AD18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="3">
         <v>1000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>300</v>
-      </c>
-      <c r="AK18" s="3">
-        <v>500</v>
       </c>
       <c r="AL18" s="3">
         <v>500</v>
       </c>
+      <c r="AM18" s="3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1952,8 +1986,8 @@
       <c r="M20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="N20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
@@ -2025,120 +2059,126 @@
         <v>0</v>
       </c>
       <c r="AL20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-900</v>
       </c>
-      <c r="E21" s="3">
-        <v>-400</v>
-      </c>
       <c r="F21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G21" s="3">
         <v>-1100</v>
       </c>
-      <c r="G21" s="3">
-        <v>-600</v>
-      </c>
       <c r="H21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1900</v>
-      </c>
-      <c r="L21" s="3">
-        <v>1600</v>
       </c>
       <c r="M21" s="3">
         <v>1600</v>
       </c>
       <c r="N21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O21" s="3">
         <v>600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>17800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-8400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>11800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2188,25 +2228,25 @@
         <v>100</v>
       </c>
       <c r="S22" s="3">
+        <v>100</v>
+      </c>
+      <c r="T22" s="3">
         <v>500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>3100</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>3200</v>
       </c>
       <c r="Z22" s="3">
         <v>3200</v>
@@ -2215,260 +2255,269 @@
         <v>3200</v>
       </c>
       <c r="AB22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AC22" s="3">
         <v>3100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>3100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>2200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>3300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>2900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>2400</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>400</v>
       </c>
       <c r="AK22" s="3">
         <v>400</v>
       </c>
       <c r="AL22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AM22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-23200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1300</v>
       </c>
-      <c r="G23" s="3">
-        <v>-21800</v>
-      </c>
       <c r="H23" s="3">
-        <v>-1900</v>
+        <v>-20700</v>
       </c>
       <c r="I23" s="3">
-        <v>-1600</v>
+        <v>-1800</v>
       </c>
       <c r="J23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1100</v>
-      </c>
-      <c r="L23" s="3">
-        <v>700</v>
       </c>
       <c r="M23" s="3">
         <v>700</v>
       </c>
       <c r="N23" s="3">
+        <v>700</v>
+      </c>
+      <c r="O23" s="3">
         <v>-300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>16600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-12200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>7300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>9800</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-900</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-6800</v>
-      </c>
-      <c r="L24" s="3">
-        <v>100</v>
       </c>
       <c r="M24" s="3">
         <v>100</v>
       </c>
       <c r="N24" s="3">
+        <v>100</v>
+      </c>
+      <c r="O24" s="3">
         <v>500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-100</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-6400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>200</v>
-      </c>
-      <c r="AJ24" s="3">
-        <v>100</v>
       </c>
       <c r="AK24" s="3">
         <v>100</v>
       </c>
       <c r="AL24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-33000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2300</v>
       </c>
-      <c r="G26" s="3">
-        <v>-19300</v>
-      </c>
       <c r="H26" s="3">
-        <v>-1000</v>
+        <v>-18100</v>
       </c>
       <c r="I26" s="3">
-        <v>-1600</v>
+        <v>-900</v>
       </c>
       <c r="J26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K26" s="3">
         <v>200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7900</v>
-      </c>
-      <c r="L26" s="3">
-        <v>700</v>
       </c>
       <c r="M26" s="3">
         <v>700</v>
       </c>
       <c r="N26" s="3">
+        <v>700</v>
+      </c>
+      <c r="O26" s="3">
         <v>-800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>16700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-12600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>7200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5400</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-3600</v>
       </c>
       <c r="Z26" s="3">
         <v>-3600</v>
       </c>
       <c r="AA26" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-33100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-19300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7900</v>
-      </c>
-      <c r="L27" s="3">
-        <v>700</v>
       </c>
       <c r="M27" s="3">
         <v>700</v>
       </c>
       <c r="N27" s="3">
+        <v>700</v>
+      </c>
+      <c r="O27" s="3">
         <v>-800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>16700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-12600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>31700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5400</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-3600</v>
       </c>
       <c r="Z27" s="3">
         <v>-3600</v>
       </c>
       <c r="AA27" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,17 +2965,20 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>-200</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
@@ -2925,10 +2986,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="I29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2972,8 +3033,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2990,21 +3051,21 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>400</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>400</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3272,8 +3342,8 @@
       <c r="M32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
+      <c r="N32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -3345,120 +3415,126 @@
         <v>0</v>
       </c>
       <c r="AL32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-33100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-19300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7900</v>
-      </c>
-      <c r="L33" s="3">
-        <v>700</v>
       </c>
       <c r="M33" s="3">
         <v>700</v>
       </c>
       <c r="N33" s="3">
+        <v>700</v>
+      </c>
+      <c r="O33" s="3">
         <v>-800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>16700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-12600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>31700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5400</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-3600</v>
       </c>
       <c r="Z33" s="3">
         <v>-3600</v>
       </c>
       <c r="AA33" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-33100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-19300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7900</v>
-      </c>
-      <c r="L35" s="3">
-        <v>700</v>
       </c>
       <c r="M35" s="3">
         <v>700</v>
       </c>
       <c r="N35" s="3">
+        <v>700</v>
+      </c>
+      <c r="O35" s="3">
         <v>-800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>16700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-12600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>31700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5400</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-3600</v>
       </c>
       <c r="Z35" s="3">
         <v>-3600</v>
       </c>
       <c r="AA35" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E41" s="3">
         <v>18500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>19600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>21200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>22500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>20700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>20100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>18500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>18800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>14300</v>
-      </c>
-      <c r="U41" s="3">
-        <v>14100</v>
       </c>
       <c r="V41" s="3">
         <v>14100</v>
       </c>
       <c r="W41" s="3">
+        <v>14100</v>
+      </c>
+      <c r="X41" s="3">
         <v>16600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4092,46 +4182,49 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E43" s="3">
         <v>11900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>14600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>18500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>19900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>20300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>22800</v>
-      </c>
-      <c r="O43" s="3">
-        <v>21200</v>
       </c>
       <c r="P43" s="3">
         <v>21200</v>
@@ -4140,70 +4233,73 @@
         <v>21200</v>
       </c>
       <c r="R43" s="3">
+        <v>21200</v>
+      </c>
+      <c r="S43" s="3">
         <v>23100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>20300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>19000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>18600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>16000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>13700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>17300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>20200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>20800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>20400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>20000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>19000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>20800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>21200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>20600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>22700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>23200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>24000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>13100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>12600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4237,8 +4333,8 @@
       <c r="M44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -4312,26 +4408,29 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>1200</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4347,193 +4446,199 @@
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3">
         <v>600</v>
-      </c>
-      <c r="O45" s="3">
-        <v>800</v>
       </c>
       <c r="P45" s="3">
         <v>800</v>
       </c>
       <c r="Q45" s="3">
+        <v>800</v>
+      </c>
+      <c r="R45" s="3">
         <v>900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>900</v>
-      </c>
-      <c r="V45" s="3">
-        <v>1400</v>
       </c>
       <c r="W45" s="3">
         <v>1400</v>
       </c>
       <c r="X45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y45" s="3">
         <v>1600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E46" s="3">
         <v>32500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>33000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>35400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>35500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>36800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>37000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>41800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>41400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>41300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>39500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>42200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>39500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>36200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>34200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>33700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>28500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>34700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>33600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>31500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>31700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>21200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>23700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>27100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>27400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>25100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>25000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>26200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>25700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>25300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>27500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>29000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>29400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>16200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>16400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>15600</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4567,8 +4672,8 @@
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -4642,82 +4747,85 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E48" s="3">
         <v>3500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4600</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>4700</v>
       </c>
       <c r="R48" s="3">
         <v>4700</v>
       </c>
       <c r="S48" s="3">
+        <v>4700</v>
+      </c>
+      <c r="T48" s="3">
         <v>4400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5100</v>
-      </c>
-      <c r="V48" s="3">
-        <v>5500</v>
       </c>
       <c r="W48" s="3">
         <v>5500</v>
       </c>
       <c r="X48" s="3">
-        <v>6300</v>
+        <v>5500</v>
       </c>
       <c r="Y48" s="3">
         <v>6300</v>
       </c>
       <c r="Z48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AA48" s="3">
         <v>900</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>800</v>
       </c>
       <c r="AB48" s="3">
         <v>800</v>
@@ -4726,7 +4834,7 @@
         <v>800</v>
       </c>
       <c r="AD48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AE48" s="3">
         <v>900</v>
@@ -4744,126 +4852,132 @@
         <v>900</v>
       </c>
       <c r="AJ48" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK48" s="3">
         <v>500</v>
       </c>
       <c r="AL48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AM48" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E49" s="3">
         <v>25700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>46600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>46800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>47000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>68300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>69000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>69700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>70400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>71100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>71900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>72600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>73300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>74000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>75000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>78200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>79200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>80200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>81200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>82300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>92300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>93400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>94800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>96200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>97600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>103300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>104700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>106100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>107500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>108900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>110200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>111600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>110300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>28900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>29300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,43 +5199,46 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>200</v>
       </c>
       <c r="F52" s="3">
+        <v>200</v>
+      </c>
+      <c r="G52" s="3">
         <v>400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>500</v>
-      </c>
-      <c r="J52" s="3">
-        <v>600</v>
       </c>
       <c r="K52" s="3">
         <v>600</v>
       </c>
       <c r="L52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="M52" s="3">
         <v>700</v>
       </c>
       <c r="N52" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="O52" s="3">
         <v>800</v>
@@ -5127,40 +5247,40 @@
         <v>800</v>
       </c>
       <c r="Q52" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="R52" s="3">
         <v>1000</v>
       </c>
       <c r="S52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T52" s="3">
         <v>1100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>700</v>
-      </c>
-      <c r="W52" s="3">
-        <v>300</v>
       </c>
       <c r="X52" s="3">
         <v>300</v>
       </c>
       <c r="Y52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Z52" s="3">
         <v>400</v>
       </c>
       <c r="AA52" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB52" s="3">
         <v>600</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>400</v>
       </c>
       <c r="AC52" s="3">
         <v>400</v>
@@ -5172,10 +5292,10 @@
         <v>400</v>
       </c>
       <c r="AF52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AG52" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AH52" s="3">
         <v>300</v>
@@ -5184,7 +5304,7 @@
         <v>300</v>
       </c>
       <c r="AJ52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AK52" s="3">
         <v>0</v>
@@ -5192,8 +5312,11 @@
       <c r="AL52" s="3">
         <v>0</v>
       </c>
+      <c r="AM52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E54" s="3">
         <v>61800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>92800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>95900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>96900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>117000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>117600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>123600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>123700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>118100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>116200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>119600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>117800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>115600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>114900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>117600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>113300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>120200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>120500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>120000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>129800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>121200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>125200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>124500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>126300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>129600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>130900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>133600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>134400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>135100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>139000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>141800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>141000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>45700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>46300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>45900</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,154 +5622,158 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>2500</v>
       </c>
       <c r="I57" s="3">
         <v>2500</v>
       </c>
       <c r="J57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K57" s="3">
         <v>2800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2500</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>2000</v>
       </c>
       <c r="AF57" s="3">
         <v>2000</v>
       </c>
       <c r="AG57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AH57" s="3">
         <v>2100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F58" s="3">
         <v>1200</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1300</v>
       </c>
       <c r="G58" s="3">
         <v>1300</v>
       </c>
       <c r="H58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I58" s="3">
         <v>1400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1500</v>
       </c>
       <c r="J58" s="3">
         <v>1500</v>
       </c>
       <c r="K58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L58" s="3">
         <v>1700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1300</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -5650,326 +5784,335 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>16700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>11000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>8800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>7900</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>1200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>17200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>16800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>15000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>12600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>14000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>8500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>10100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E59" s="3">
+        <v>800</v>
+      </c>
+      <c r="F59" s="3">
         <v>1000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>15400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>14400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>7400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>13800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>12500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>5000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E60" s="3">
         <v>8400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>15600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>31200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>23400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>26000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>22100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>18200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>24800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>13400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>18600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>15900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>14000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>13500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>13100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>27800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>26300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>26900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>19500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>27900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>14800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>16400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G61" s="3">
         <v>2400</v>
       </c>
-      <c r="E61" s="3">
-        <v>2100</v>
-      </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I61" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J61" s="3">
         <v>2400</v>
       </c>
-      <c r="G61" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H61" s="3">
-        <v>2200</v>
-      </c>
-      <c r="I61" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2500</v>
-      </c>
-      <c r="K61" s="3">
-        <v>3100</v>
       </c>
       <c r="L61" s="3">
         <v>3100</v>
       </c>
       <c r="M61" s="3">
+        <v>3100</v>
+      </c>
+      <c r="N61" s="3">
         <v>2000</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -5983,72 +6126,75 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>7000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>62500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>65000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>67400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>60700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>74900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>72500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>68200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>69800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>69900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>68800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>69900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>55000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>56000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>58500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>67600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>59000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>4900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>4800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>8</v>
@@ -6065,59 +6211,59 @@
       <c r="I62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
         <v>400</v>
-      </c>
-      <c r="K62" s="3">
-        <v>200</v>
       </c>
       <c r="L62" s="3">
         <v>200</v>
       </c>
       <c r="M62" s="3">
+        <v>200</v>
+      </c>
+      <c r="N62" s="3">
         <v>500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4600</v>
-      </c>
-      <c r="X62" s="3">
-        <v>4900</v>
       </c>
       <c r="Y62" s="3">
         <v>4900</v>
       </c>
       <c r="Z62" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AA62" s="3">
         <v>900</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>1200</v>
       </c>
       <c r="AB62" s="3">
         <v>1200</v>
@@ -6126,25 +6272,25 @@
         <v>1200</v>
       </c>
       <c r="AD62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AE62" s="3">
         <v>700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4700</v>
-      </c>
-      <c r="AJ62" s="3">
-        <v>200</v>
       </c>
       <c r="AK62" s="3">
         <v>200</v>
@@ -6152,8 +6298,11 @@
       <c r="AL62" s="3">
         <v>200</v>
       </c>
+      <c r="AM62" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E66" s="3">
         <v>11100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>36800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>35600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>94300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>93100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>92600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>90100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>91500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>90900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>87700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>86900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>85100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>83500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>83700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>84500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>84100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>86500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>88400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>91600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>19800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>21500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6918,13 +7086,13 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
-        <v>27700</v>
+        <v>0</v>
       </c>
       <c r="Y70" s="3">
         <v>27700</v>
       </c>
       <c r="Z70" s="3">
-        <v>27600</v>
+        <v>27700</v>
       </c>
       <c r="AA70" s="3">
         <v>27600</v>
@@ -6936,7 +7104,7 @@
         <v>27600</v>
       </c>
       <c r="AD70" s="3">
-        <v>28800</v>
+        <v>27600</v>
       </c>
       <c r="AE70" s="3">
         <v>28800</v>
@@ -6945,7 +7113,7 @@
         <v>28800</v>
       </c>
       <c r="AG70" s="3">
-        <v>29300</v>
+        <v>28800</v>
       </c>
       <c r="AH70" s="3">
         <v>29300</v>
@@ -6954,7 +7122,7 @@
         <v>29300</v>
       </c>
       <c r="AJ70" s="3">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="AK70" s="3">
         <v>0</v>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-59500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-26400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-25700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-23500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-4200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-9700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-10400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-11000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-10300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-14000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-30600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-33600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-32700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-31000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-30700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-18100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-49800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-44300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-40800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-37200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-30400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-26500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-23000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-22000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-20100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-17200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-15500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-19200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-13200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-13000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E76" s="3">
         <v>50600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>83600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>84200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>86300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>105500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>106300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>109300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>110400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>102800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>102000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>101000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>101600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>98800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>97600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>80800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>77600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>25900</v>
-      </c>
-      <c r="U76" s="3">
-        <v>27400</v>
       </c>
       <c r="V76" s="3">
         <v>27400</v>
       </c>
       <c r="W76" s="3">
+        <v>27400</v>
+      </c>
+      <c r="X76" s="3">
         <v>39700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>16900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>19900</v>
-      </c>
-      <c r="AD76" s="3">
-        <v>21100</v>
       </c>
       <c r="AE76" s="3">
         <v>21100</v>
       </c>
       <c r="AF76" s="3">
+        <v>21100</v>
+      </c>
+      <c r="AG76" s="3">
         <v>22200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>23200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>24100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>20100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>25800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>24800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-33100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-19300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7900</v>
-      </c>
-      <c r="L81" s="3">
-        <v>700</v>
       </c>
       <c r="M81" s="3">
         <v>700</v>
       </c>
       <c r="N81" s="3">
+        <v>700</v>
+      </c>
+      <c r="O81" s="3">
         <v>-800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>16700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-12600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>31700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5400</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-3600</v>
       </c>
       <c r="Z81" s="3">
         <v>-3600</v>
       </c>
       <c r="AA81" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,13 +8195,14 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E83" s="3">
         <v>400</v>
@@ -8012,10 +8211,10 @@
         <v>400</v>
       </c>
       <c r="G83" s="3">
+        <v>400</v>
+      </c>
+      <c r="H83" s="3">
         <v>1100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>100</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
@@ -8033,13 +8232,13 @@
         <v>100</v>
       </c>
       <c r="N83" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="O83" s="3">
         <v>800</v>
       </c>
       <c r="P83" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="Q83" s="3">
         <v>1100</v>
@@ -8057,13 +8256,13 @@
         <v>1100</v>
       </c>
       <c r="V83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="W83" s="3">
         <v>1200</v>
       </c>
       <c r="X83" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="Y83" s="3">
         <v>1500</v>
@@ -8093,13 +8292,13 @@
         <v>1500</v>
       </c>
       <c r="AH83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AI83" s="3">
         <v>1300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1700</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>400</v>
       </c>
       <c r="AK83" s="3">
         <v>400</v>
@@ -8107,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>400</v>
       </c>
+      <c r="AM83" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>100</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>-2500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-600</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>800</v>
       </c>
       <c r="AD89" s="3">
         <v>800</v>
       </c>
       <c r="AE89" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF89" s="3">
         <v>500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,8 +9027,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8840,7 +9061,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
@@ -8861,7 +9082,7 @@
         <v>-100</v>
       </c>
       <c r="T91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -8876,13 +9097,13 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z91" s="3">
         <v>-100</v>
       </c>
       <c r="AA91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -8891,23 +9112,23 @@
         <v>0</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
       <c r="AF91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG91" s="3">
         <v>-100</v>
       </c>
       <c r="AH91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-200</v>
       </c>
-      <c r="AI91" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
@@ -8915,10 +9136,13 @@
         <v>0</v>
       </c>
       <c r="AL91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,17 +9364,20 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1000</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
@@ -9170,7 +9400,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N94" s="3">
         <v>-100</v>
@@ -9191,7 +9421,7 @@
         <v>-100</v>
       </c>
       <c r="T94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -9206,13 +9436,13 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z94" s="3">
         <v>-100</v>
       </c>
       <c r="AA94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB94" s="3">
         <v>0</v>
@@ -9221,34 +9451,37 @@
         <v>0</v>
       </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
       <c r="AF94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG94" s="3">
         <v>-100</v>
       </c>
       <c r="AH94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-24800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-500</v>
-      </c>
-      <c r="AK94" s="3">
-        <v>-100</v>
       </c>
       <c r="AL94" s="3">
         <v>-100</v>
       </c>
+      <c r="AM94" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9322,8 +9556,8 @@
       <c r="M96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,8 +9970,11 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9739,29 +9985,29 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
-        <v>-1600</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3">
         <v>-1600</v>
       </c>
       <c r="K100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="L100" s="3">
         <v>-500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
@@ -9778,11 +10024,11 @@
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>-4400</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
@@ -9790,55 +10036,58 @@
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>11900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>26700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9872,8 +10121,8 @@
       <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -9947,114 +10196,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>100</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>-2500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>14200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
   <si>
     <t>JOB</t>
   </si>
@@ -656,505 +656,530 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>23500</v>
+      </c>
+      <c r="F8" s="3">
         <v>24500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>24500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>24000</v>
       </c>
-      <c r="G8" s="3">
-        <v>28300</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3">
         <v>27000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>25600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>28100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>34300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>38200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>38900</v>
-      </c>
-      <c r="N8" s="3">
-        <v>41100</v>
-      </c>
-      <c r="O8" s="3">
-        <v>41500</v>
       </c>
       <c r="P8" s="3">
         <v>41100</v>
       </c>
       <c r="Q8" s="3">
+        <v>41500</v>
+      </c>
+      <c r="R8" s="3">
+        <v>41100</v>
+      </c>
+      <c r="S8" s="3">
         <v>39600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>42800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>41500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>38100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>34700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>34600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>31000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>26600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>34700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>37600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>38900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>38100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>36200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>38500</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>39900</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>40300</v>
       </c>
       <c r="AG8" s="3">
         <v>39900</v>
       </c>
       <c r="AH8" s="3">
+        <v>40300</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>39900</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>45200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>46400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>46100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>21500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>21000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>15100</v>
+      </c>
+      <c r="F9" s="3">
         <v>15800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>16100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>16100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3">
+        <v>17800</v>
+      </c>
+      <c r="K9" s="3">
+        <v>17200</v>
+      </c>
+      <c r="L9" s="3">
         <v>18800</v>
       </c>
-      <c r="H9" s="3">
-        <v>17800</v>
-      </c>
-      <c r="I9" s="3">
-        <v>17200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>18800</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>22700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>24500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>25600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>26800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>26400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>24600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>25100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>27300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>26200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>24200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>23800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>22100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>20500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>16900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>22800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>25000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>25600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>24500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>24500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>25800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>25100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>25500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>26200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>29500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>29500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>29000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>15900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>15600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>8700</v>
+        <v>7400</v>
       </c>
       <c r="E10" s="3">
         <v>8400</v>
       </c>
       <c r="F10" s="3">
+        <v>8700</v>
+      </c>
+      <c r="G10" s="3">
+        <v>8400</v>
+      </c>
+      <c r="H10" s="3">
         <v>7900</v>
       </c>
-      <c r="G10" s="3">
-        <v>9500</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3">
         <v>9200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>8400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>9300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>11600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>13700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>13200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>14400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>15100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>16500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>14500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>15500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>15300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>13900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>10900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>12500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>10500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>9700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>11900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>12600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>13300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>13600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>11700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>12700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>14800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>14800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>13700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>15700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>16900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>17100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>5600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>5400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1194,8 +1219,10 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1307,8 +1334,14 @@
       <c r="AM12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1420,129 +1453,141 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
+        <v>100</v>
+      </c>
+      <c r="G14" s="3">
         <v>22000</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>19500</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>700</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>2000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>-14100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-1100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>2200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>9900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>-10800</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>400</v>
       </c>
       <c r="AA14" s="3">
         <v>1300</v>
       </c>
       <c r="AB14" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AD14" s="3">
         <v>4900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>1200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>200</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>600</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AL14" s="3">
         <v>3200</v>
-      </c>
-      <c r="AK14" s="3">
-        <v>100</v>
-      </c>
-      <c r="AL14" s="3">
-        <v>0</v>
       </c>
       <c r="AM14" s="3">
         <v>100</v>
       </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
         <v>300</v>
@@ -1551,10 +1596,10 @@
         <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
         <v>800</v>
@@ -1578,10 +1623,10 @@
         <v>800</v>
       </c>
       <c r="Q15" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="R15" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="S15" s="3">
         <v>1100</v>
@@ -1596,16 +1641,16 @@
         <v>1100</v>
       </c>
       <c r="W15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y15" s="3">
         <v>1200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>1500</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>1500</v>
       </c>
       <c r="AA15" s="3">
         <v>1500</v>
@@ -1632,22 +1677,28 @@
         <v>1500</v>
       </c>
       <c r="AI15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AK15" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>1700</v>
-      </c>
-      <c r="AK15" s="3">
-        <v>400</v>
-      </c>
-      <c r="AL15" s="3">
-        <v>400</v>
       </c>
       <c r="AM15" s="3">
         <v>400</v>
       </c>
+      <c r="AN15" s="3">
+        <v>400</v>
+      </c>
+      <c r="AO15" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,234 +1735,248 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>24200</v>
+      </c>
+      <c r="F17" s="3">
         <v>25000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>25700</v>
       </c>
-      <c r="F17" s="3">
-        <v>24800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>29700</v>
-      </c>
       <c r="H17" s="3">
+        <v>24700</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3">
         <v>28300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>27500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>29800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>34100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>37100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>38100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>40300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>41700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>38300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>38500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>26100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>38000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>38500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>33800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>32700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>40600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>16000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>37000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>37700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>39200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>41900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>37000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>38500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>38900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>39700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>39800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>43800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>46100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>49500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>21200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>20500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="M18" s="3">
+        <v>200</v>
+      </c>
+      <c r="N18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O18" s="3">
+        <v>800</v>
+      </c>
+      <c r="P18" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="S18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T18" s="3">
+        <v>16700</v>
+      </c>
+      <c r="U18" s="3">
+        <v>3500</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="W18" s="3">
+        <v>900</v>
+      </c>
+      <c r="X18" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>10600</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="K18" s="3">
-        <v>200</v>
-      </c>
-      <c r="L18" s="3">
-        <v>1100</v>
-      </c>
-      <c r="M18" s="3">
-        <v>800</v>
-      </c>
-      <c r="N18" s="3">
-        <v>800</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P18" s="3">
-        <v>2800</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>1100</v>
-      </c>
-      <c r="R18" s="3">
-        <v>16700</v>
-      </c>
-      <c r="S18" s="3">
-        <v>3500</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-400</v>
-      </c>
-      <c r="U18" s="3">
-        <v>900</v>
-      </c>
-      <c r="V18" s="3">
-        <v>1900</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="X18" s="3">
-        <v>10600</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="3">
         <v>1000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>1400</v>
-      </c>
-      <c r="AI18" s="3">
-        <v>300</v>
-      </c>
-      <c r="AJ18" s="3">
-        <v>-3400</v>
       </c>
       <c r="AK18" s="3">
         <v>300</v>
       </c>
       <c r="AL18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="AM18" s="3">
+        <v>300</v>
+      </c>
+      <c r="AN18" s="3">
         <v>500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1951,13 +2016,15 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>-200</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>8</v>
@@ -1989,11 +2056,11 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -2062,123 +2129,135 @@
         <v>0</v>
       </c>
       <c r="AM20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>200</v>
+      </c>
+      <c r="J21" s="3">
         <v>-500</v>
       </c>
-      <c r="G21" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>3600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>2300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>17800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>4600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>2000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>3100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-8400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>11800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>1500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>2500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>2100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>1500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>3000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2197,8 +2276,8 @@
       <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
-        <v>100</v>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
@@ -2231,37 +2310,37 @@
         <v>100</v>
       </c>
       <c r="T22" s="3">
+        <v>100</v>
+      </c>
+      <c r="U22" s="3">
+        <v>100</v>
+      </c>
+      <c r="V22" s="3">
         <v>500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>2500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>2700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>2600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>3300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>3100</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>3200</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>3200</v>
       </c>
       <c r="AB22" s="3">
         <v>3200</v>
       </c>
       <c r="AC22" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="AD22" s="3">
-        <v>2900</v>
+        <v>3200</v>
       </c>
       <c r="AE22" s="3">
         <v>3100</v>
@@ -2270,254 +2349,272 @@
         <v>2900</v>
       </c>
       <c r="AG22" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AI22" s="3">
         <v>2200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>3300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>2400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-23200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3">
         <v>-20700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>16600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>3400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-1000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-1600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-12200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>7300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>-100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G24" s="3">
         <v>9800</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>900</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3">
         <v>-2500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-900</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-6800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
-      </c>
-      <c r="N24" s="3">
-        <v>100</v>
-      </c>
-      <c r="O24" s="3">
-        <v>500</v>
       </c>
       <c r="P24" s="3">
         <v>100</v>
       </c>
       <c r="Q24" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="R24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>200</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-100</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>-6400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2629,234 +2726,252 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-33000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-700</v>
       </c>
-      <c r="G26" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3">
         <v>-18100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>7900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>2600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>16700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>3000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-12600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>7200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-6800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>-100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-33100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3">
         <v>-19300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>7900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>2600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>16700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>3000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-1700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-12600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>31700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-6800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>-100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2968,8 +3083,14 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2977,26 +3098,26 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>100</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-200</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-1200</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>-100</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
@@ -3036,11 +3157,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3054,24 +3175,24 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>400</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>400</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3081,8 +3202,14 @@
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3194,8 +3321,14 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3307,13 +3440,19 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>200</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>8</v>
@@ -3345,11 +3484,11 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -3418,123 +3557,135 @@
         <v>0</v>
       </c>
       <c r="AM32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-33100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-700</v>
       </c>
-      <c r="G33" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3">
         <v>-19300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>7900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>2600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>16700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>3000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-12600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>31700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-6800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>-100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3646,239 +3797,257 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-33100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-700</v>
       </c>
-      <c r="G35" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3">
         <v>-19300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>7900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>2600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>16700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>3000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-12600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>31700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-6800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>-100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3918,8 +4087,10 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3959,121 +4130,129 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>21400</v>
+      </c>
+      <c r="F41" s="3">
         <v>18600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>18500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>19700</v>
       </c>
-      <c r="G41" s="3">
-        <v>20800</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
+        <v>20700</v>
+      </c>
+      <c r="J41" s="3">
         <v>19600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>21200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>19900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>22500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>20700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>20100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>18500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>18800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>17500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>14200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>12100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>9900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>7400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>14300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>14100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>14100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>16600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>4100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>4200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>2800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>3500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>3200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>2600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>2900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>3500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>2900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>1600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>2200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4185,121 +4364,133 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F43" s="3">
         <v>11800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>11900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>12300</v>
       </c>
-      <c r="G43" s="3">
-        <v>13700</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>12800</v>
+      </c>
+      <c r="J43" s="3">
         <v>14600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>14200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>15900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>18500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>19900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>20400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>20300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>22800</v>
-      </c>
-      <c r="P43" s="3">
-        <v>21200</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>21200</v>
       </c>
       <c r="R43" s="3">
         <v>21200</v>
       </c>
       <c r="S43" s="3">
+        <v>21200</v>
+      </c>
+      <c r="T43" s="3">
+        <v>21200</v>
+      </c>
+      <c r="U43" s="3">
         <v>23100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>20300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>19000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>18600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>16000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>13700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>17300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>20200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>20800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>20400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>20000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>19000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>20800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>21200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>20600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>22700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>23200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>24000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>13100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>12600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4336,11 +4527,11 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4411,32 +4602,38 @@
       <c r="AM44" s="3">
         <v>0</v>
       </c>
+      <c r="AN44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>1200</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4449,196 +4646,208 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>800</v>
-      </c>
-      <c r="U45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="V45" s="3">
-        <v>900</v>
       </c>
       <c r="W45" s="3">
         <v>1400</v>
       </c>
       <c r="X45" s="3">
+        <v>900</v>
+      </c>
+      <c r="Y45" s="3">
         <v>1400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AA45" s="3">
         <v>1600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>2200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>2800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>2400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>2500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>2300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>1900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>1800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>1400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>2500</v>
-      </c>
-      <c r="AK45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AL45" s="3">
-        <v>1600</v>
       </c>
       <c r="AM45" s="3">
         <v>1500</v>
       </c>
+      <c r="AN45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AO45" s="3">
+        <v>1500</v>
+      </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E46" s="3">
         <v>31700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
+        <v>31700</v>
+      </c>
+      <c r="G46" s="3">
         <v>32500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>33000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>35400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>35500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>36800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>37000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>41800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>41400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>41300</v>
-      </c>
-      <c r="N46" s="3">
-        <v>39500</v>
-      </c>
-      <c r="O46" s="3">
-        <v>42200</v>
       </c>
       <c r="P46" s="3">
         <v>39500</v>
       </c>
       <c r="Q46" s="3">
+        <v>42200</v>
+      </c>
+      <c r="R46" s="3">
+        <v>39500</v>
+      </c>
+      <c r="S46" s="3">
         <v>36200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>34200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>33700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>28500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>34700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>33600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>31500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>31700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>21200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>23700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>27100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>27400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>25100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>25000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>26200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>25700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>25300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>27500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>29000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>29400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>16200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>16400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>15600</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4675,11 +4884,11 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4750,97 +4959,103 @@
       <c r="AM47" s="3">
         <v>0</v>
       </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F48" s="3">
         <v>3200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3500</v>
-      </c>
-      <c r="F48" s="3">
-        <v>3400</v>
-      </c>
-      <c r="G48" s="3">
-        <v>3800</v>
       </c>
       <c r="H48" s="3">
         <v>3400</v>
       </c>
       <c r="I48" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K48" s="3">
         <v>3800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>4500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>5000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>4000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>4200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>4600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>4700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>4700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>4400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>4900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>5100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>5500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>5500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>6300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>6300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>900</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>800</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>800</v>
       </c>
       <c r="AD48" s="3">
         <v>800</v>
       </c>
       <c r="AE48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AF48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AG48" s="3">
         <v>900</v>
@@ -4855,129 +5070,141 @@
         <v>900</v>
       </c>
       <c r="AK48" s="3">
+        <v>900</v>
+      </c>
+      <c r="AL48" s="3">
+        <v>900</v>
+      </c>
+      <c r="AM48" s="3">
         <v>500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>25400</v>
+      </c>
+      <c r="F49" s="3">
         <v>25600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>25700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>46600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>46800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>47000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>68300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>69000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>69700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>70400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>71100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>71900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>72600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>73300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>74000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>75000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>78200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>79200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>80200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>81200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>82300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>92300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>93400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>94800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>96200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>97600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>103300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>104700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>106100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>107500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>108900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>110200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>111600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>110300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>28900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>29300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5089,8 +5316,14 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5202,91 +5435,97 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>200</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
+        <v>100</v>
+      </c>
+      <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
+        <v>600</v>
+      </c>
+      <c r="J52" s="3">
+        <v>300</v>
+      </c>
+      <c r="K52" s="3">
         <v>400</v>
       </c>
-      <c r="H52" s="3">
-        <v>300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>400</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>700</v>
-      </c>
-      <c r="O52" s="3">
-        <v>800</v>
-      </c>
-      <c r="P52" s="3">
-        <v>800</v>
       </c>
       <c r="Q52" s="3">
         <v>800</v>
       </c>
       <c r="R52" s="3">
+        <v>800</v>
+      </c>
+      <c r="S52" s="3">
+        <v>800</v>
+      </c>
+      <c r="T52" s="3">
         <v>1000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>400</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>400</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>600</v>
       </c>
       <c r="AC52" s="3">
         <v>400</v>
       </c>
       <c r="AD52" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AE52" s="3">
         <v>400</v>
@@ -5295,28 +5534,34 @@
         <v>400</v>
       </c>
       <c r="AG52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AH52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AI52" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AJ52" s="3">
         <v>300</v>
       </c>
       <c r="AK52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AL52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AM52" s="3">
         <v>0</v>
       </c>
+      <c r="AN52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5428,121 +5673,133 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>60000</v>
+      </c>
+      <c r="F54" s="3">
         <v>60600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>61800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>92800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>95900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>96900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>117000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>117600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>123600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>123700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>118100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>116200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>119600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>117800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>115600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>114900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>117600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>113300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>120200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>120500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>120000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>129800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>121200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>125200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>124500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>126300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>129600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>130900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>133600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>134400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>135100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>139000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>141800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>141000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>45700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>46300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>45900</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5582,8 +5839,10 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5623,163 +5882,171 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G57" s="3">
         <v>1900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2800</v>
-      </c>
-      <c r="L57" s="3">
-        <v>2900</v>
-      </c>
-      <c r="M57" s="3">
-        <v>3400</v>
       </c>
       <c r="N57" s="3">
         <v>2900</v>
       </c>
       <c r="O57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="P57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Q57" s="3">
         <v>3000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>2300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>2100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>2600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>2500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>2900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>3700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>9100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>3900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>2900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>2500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>2000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>2000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>2100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>3200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>1400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>1300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>1600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="E58" s="3">
         <v>1300</v>
       </c>
       <c r="F58" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="G58" s="3">
         <v>1300</v>
       </c>
       <c r="H58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J58" s="3">
         <v>1300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1300</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -5787,81 +6054,87 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>16700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>11000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>8800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>5600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>2200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>7900</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
         <v>1200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>5700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>3900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>2200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>3200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>2400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>17200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>16800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>15000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>12600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>14000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>8500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>10100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>300</v>
+      </c>
+      <c r="F59" s="3">
         <v>800</v>
-      </c>
-      <c r="E59" s="3">
-        <v>800</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1000</v>
       </c>
       <c r="G59" s="3">
         <v>800</v>
@@ -5870,255 +6143,267 @@
         <v>1000</v>
       </c>
       <c r="I59" s="3">
+        <v>700</v>
+      </c>
+      <c r="J59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K59" s="3">
         <v>1100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>12600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>10400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>11600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>11300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>12200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>10600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>15400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>14600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>13900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>14400</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>9200</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>9300</v>
       </c>
       <c r="AA59" s="3">
         <v>9200</v>
       </c>
       <c r="AB59" s="3">
+        <v>9300</v>
+      </c>
+      <c r="AC59" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AD59" s="3">
         <v>2900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>7900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>7400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>8200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>8600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>7400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>9800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>13800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>12500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>5000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>4800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F60" s="3">
         <v>7600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>8400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>9300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>8600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>9400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>8900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>11500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>10100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>11400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>11000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>15600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>12900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>13300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>13600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>31200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>23400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>26000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>22100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>18200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>24800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>11700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>13400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>18600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>15900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>14000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>13500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>13100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>27800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>26300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>26900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>19500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>27900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>14800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>16400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F61" s="3">
         <v>2300</v>
       </c>
-      <c r="E61" s="3">
-        <v>2600</v>
-      </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H61" s="3">
         <v>2100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K61" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L61" s="3">
         <v>2400</v>
       </c>
-      <c r="H61" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I61" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J61" s="3">
-        <v>2400</v>
-      </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>3100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>3100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -6129,67 +6414,73 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>7000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>62500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>65000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>67400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>60700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>74900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>72500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>68200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>69800</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>69900</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>68800</v>
       </c>
       <c r="AE61" s="3">
         <v>69900</v>
       </c>
       <c r="AF61" s="3">
+        <v>68800</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>69900</v>
+      </c>
+      <c r="AH61" s="3">
         <v>55000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>56000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>58500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>67600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>59000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>4900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>4800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6208,101 +6499,107 @@
       <c r="H62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
+      <c r="I62" s="3">
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>3700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>5700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>5200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>5800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>6000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>7100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>4600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>4900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>4900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>900</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>1200</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>1200</v>
       </c>
       <c r="AD62" s="3">
         <v>1200</v>
       </c>
       <c r="AE62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AF62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AG62" s="3">
         <v>700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>1900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>1100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>4700</v>
-      </c>
-      <c r="AK62" s="3">
-        <v>200</v>
-      </c>
-      <c r="AL62" s="3">
-        <v>200</v>
       </c>
       <c r="AM62" s="3">
         <v>200</v>
       </c>
+      <c r="AN62" s="3">
+        <v>200</v>
+      </c>
+      <c r="AO62" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6414,8 +6711,14 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6527,8 +6830,14 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6640,121 +6949,133 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F66" s="3">
         <v>10200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>11100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>9200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>11700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>10500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>11500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>11300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>14300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>13300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>15300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>14100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>18600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>16200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>16800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>17300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>36800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>35600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>94300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>93100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>92600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>90100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>91500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>90900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>87700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>86900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>85100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>83500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>83700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>84500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>84100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>86500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>88400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>91600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>19800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>21500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6794,8 +7115,10 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6907,8 +7230,14 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7020,8 +7349,14 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7089,16 +7424,16 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
         <v>27700</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AB70" s="3">
         <v>27700</v>
-      </c>
-      <c r="AA70" s="3">
-        <v>27600</v>
-      </c>
-      <c r="AB70" s="3">
-        <v>27600</v>
       </c>
       <c r="AC70" s="3">
         <v>27600</v>
@@ -7107,34 +7442,40 @@
         <v>27600</v>
       </c>
       <c r="AE70" s="3">
-        <v>28800</v>
+        <v>27600</v>
       </c>
       <c r="AF70" s="3">
-        <v>28800</v>
+        <v>27600</v>
       </c>
       <c r="AG70" s="3">
         <v>28800</v>
       </c>
       <c r="AH70" s="3">
-        <v>29300</v>
+        <v>28800</v>
       </c>
       <c r="AI70" s="3">
-        <v>29300</v>
+        <v>28800</v>
       </c>
       <c r="AJ70" s="3">
         <v>29300</v>
       </c>
       <c r="AK70" s="3">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="AL70" s="3">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7246,121 +7587,133 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-60600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-60500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-60000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-59500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-26400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-25700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-23500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-4200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-3200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-9700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-10400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-11000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-12900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-14000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-30600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-33600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-32700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-31000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-30700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-18100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-49800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-44300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-40800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-37200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-30400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-26500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-23000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-22000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-20100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-17200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>-15500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>-19200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>-13200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>-13000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7472,8 +7825,14 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7585,8 +7944,14 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7698,121 +8063,133 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>50000</v>
+      </c>
+      <c r="F76" s="3">
         <v>50400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>50600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>83600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>84200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>86300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>105500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>106300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>109300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>110400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>102800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>102000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>101000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>101600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>98800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>97600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>80800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>77600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>25900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>27400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>27400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>39700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>2000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>6600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>9200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>11900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>16900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>19900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>21100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>21100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>22200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>23200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>24100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>20100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>25800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>24800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7924,239 +8301,257 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-33100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-700</v>
       </c>
-      <c r="G81" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3">
         <v>-19300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>7900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>2600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>16700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>3000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-12600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>31700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-6800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>-100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8196,16 +8591,18 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>400</v>
       </c>
-      <c r="E83" s="3">
-        <v>400</v>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F83" s="3">
         <v>400</v>
@@ -8214,13 +8611,13 @@
         <v>400</v>
       </c>
       <c r="H83" s="3">
+        <v>400</v>
+      </c>
+      <c r="I83" s="3">
+        <v>400</v>
+      </c>
+      <c r="J83" s="3">
         <v>1100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
@@ -8235,16 +8632,16 @@
         <v>100</v>
       </c>
       <c r="O83" s="3">
+        <v>100</v>
+      </c>
+      <c r="P83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q83" s="3">
         <v>800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>800</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>1100</v>
-      </c>
-      <c r="R83" s="3">
-        <v>1100</v>
       </c>
       <c r="S83" s="3">
         <v>1100</v>
@@ -8259,16 +8656,16 @@
         <v>1100</v>
       </c>
       <c r="W83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y83" s="3">
         <v>1200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>1500</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>1500</v>
       </c>
       <c r="AA83" s="3">
         <v>1500</v>
@@ -8295,22 +8692,28 @@
         <v>1500</v>
       </c>
       <c r="AI83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AJ83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AK83" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>1700</v>
-      </c>
-      <c r="AK83" s="3">
-        <v>400</v>
-      </c>
-      <c r="AL83" s="3">
-        <v>400</v>
       </c>
       <c r="AM83" s="3">
         <v>400</v>
       </c>
+      <c r="AN83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AO83" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8422,8 +8825,14 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8535,8 +8944,14 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8648,8 +9063,14 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8761,8 +9182,14 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8874,121 +9301,133 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="3">
         <v>-700</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
         <v>-1100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K89" s="3">
         <v>1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M89" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N89" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O89" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R89" s="3">
+        <v>3500</v>
+      </c>
+      <c r="S89" s="3">
+        <v>2200</v>
+      </c>
+      <c r="T89" s="3">
+        <v>2300</v>
+      </c>
+      <c r="U89" s="3">
+        <v>2600</v>
+      </c>
+      <c r="V89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="W89" s="3">
+        <v>100</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-1500</v>
       </c>
-      <c r="I89" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-900</v>
-      </c>
-      <c r="K89" s="3">
-        <v>3300</v>
-      </c>
-      <c r="L89" s="3">
-        <v>1200</v>
-      </c>
-      <c r="M89" s="3">
-        <v>1700</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="O89" s="3">
-        <v>1500</v>
-      </c>
-      <c r="P89" s="3">
-        <v>3500</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>2200</v>
-      </c>
-      <c r="R89" s="3">
-        <v>2300</v>
-      </c>
-      <c r="S89" s="3">
-        <v>2600</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="AC89" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AE89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG89" s="3">
+        <v>800</v>
+      </c>
+      <c r="AH89" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI89" s="3">
+        <v>400</v>
+      </c>
+      <c r="AJ89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AK89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AL89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AM89" s="3">
+        <v>400</v>
+      </c>
+      <c r="AN89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AO89" s="3">
         <v>100</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="X89" s="3">
-        <v>2300</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>200</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>-600</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>800</v>
-      </c>
-      <c r="AE89" s="3">
-        <v>800</v>
-      </c>
-      <c r="AF89" s="3">
-        <v>500</v>
-      </c>
-      <c r="AG89" s="3">
-        <v>400</v>
-      </c>
-      <c r="AH89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AI89" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AJ89" s="3">
-        <v>-600</v>
-      </c>
-      <c r="AK89" s="3">
-        <v>400</v>
-      </c>
-      <c r="AL89" s="3">
-        <v>-700</v>
-      </c>
-      <c r="AM89" s="3">
-        <v>100</v>
-      </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9028,16 +9467,18 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -9048,8 +9489,8 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -9064,10 +9505,10 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>-100</v>
@@ -9085,10 +9526,10 @@
         <v>-100</v>
       </c>
       <c r="U91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -9100,22 +9541,22 @@
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
       <c r="AE91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF91" s="3">
         <v>0</v>
@@ -9124,25 +9565,31 @@
         <v>-100</v>
       </c>
       <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK91" s="3">
-        <v>0</v>
-      </c>
       <c r="AL91" s="3">
         <v>0</v>
       </c>
       <c r="AM91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9254,8 +9701,14 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9367,28 +9820,34 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3">
         <v>700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1000</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
@@ -9403,10 +9862,10 @@
         <v>0</v>
       </c>
       <c r="N94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P94" s="3">
         <v>-100</v>
@@ -9424,10 +9883,10 @@
         <v>-100</v>
       </c>
       <c r="U94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -9439,22 +9898,22 @@
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
       <c r="AD94" s="3">
         <v>0</v>
       </c>
       <c r="AE94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF94" s="3">
         <v>0</v>
@@ -9463,25 +9922,31 @@
         <v>-100</v>
       </c>
       <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-24800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9521,8 +9986,10 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9559,11 +10026,11 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9634,8 +10101,14 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9747,8 +10220,14 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9860,8 +10339,14 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9973,47 +10458,53 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
         <v>0</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="M100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="N100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-500</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
@@ -10027,67 +10518,73 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-4400</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>11900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>2200</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>-500</v>
       </c>
       <c r="AE100" s="3">
         <v>-100</v>
       </c>
       <c r="AF100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-800</v>
-      </c>
-      <c r="AG100" s="3">
-        <v>-900</v>
-      </c>
-      <c r="AH100" s="3">
-        <v>1100</v>
       </c>
       <c r="AI100" s="3">
         <v>-900</v>
       </c>
       <c r="AJ100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AK100" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AL100" s="3">
         <v>26700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10124,11 +10621,11 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10199,117 +10696,129 @@
       <c r="AM101" s="3">
         <v>0</v>
       </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1100</v>
       </c>
-      <c r="G102" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-2600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>3400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>2000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>2200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>2600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-6900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>100</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-2500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>14200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>1400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>1300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>-1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
   <si>
     <t>JOB</t>
   </si>
@@ -656,411 +656,421 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E8" s="3">
         <v>20500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>23500</v>
-      </c>
-      <c r="F8" s="3">
-        <v>24500</v>
       </c>
       <c r="G8" s="3">
         <v>24500</v>
       </c>
       <c r="H8" s="3">
+        <v>24500</v>
+      </c>
+      <c r="I8" s="3">
         <v>24000</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>27000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>25600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>28100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>34300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>38200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>38900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>41100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>41500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>41100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>39600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>42800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>41500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>38100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>34700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>34600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>31000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>26600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>34700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>37600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>38900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>38100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>36200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>38500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>39900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>40300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>39900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>45200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>46400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>46100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>21500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>21000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E9" s="3">
         <v>13100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15800</v>
-      </c>
-      <c r="G9" s="3">
-        <v>16100</v>
       </c>
       <c r="H9" s="3">
         <v>16100</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="I9" s="3">
+        <v>16100</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>17800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>17200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>22700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>24500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>25600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>24600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>25100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>27300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>26200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>24200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>23800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>22100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>20500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>16900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>22800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>25000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>25600</v>
-      </c>
-      <c r="AD9" s="3">
-        <v>24500</v>
       </c>
       <c r="AE9" s="3">
         <v>24500</v>
       </c>
       <c r="AF9" s="3">
+        <v>24500</v>
+      </c>
+      <c r="AG9" s="3">
         <v>25800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>25100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>25500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>26200</v>
-      </c>
-      <c r="AJ9" s="3">
-        <v>29500</v>
       </c>
       <c r="AK9" s="3">
         <v>29500</v>
       </c>
       <c r="AL9" s="3">
+        <v>29500</v>
+      </c>
+      <c r="AM9" s="3">
         <v>29000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>15900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>15600</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1068,118 +1078,121 @@
         <v>7400</v>
       </c>
       <c r="E10" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F10" s="3">
         <v>8400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7900</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>9200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>14400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>15100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>16500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>14500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>15500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>15300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>13900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>10900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>12500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>10500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>11900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>12600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>13300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>13600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>11700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>12700</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>14800</v>
       </c>
       <c r="AH10" s="3">
         <v>14800</v>
       </c>
       <c r="AI10" s="3">
+        <v>14800</v>
+      </c>
+      <c r="AJ10" s="3">
         <v>13700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>15700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>16900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>17100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>5600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>5400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,8 +1234,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1340,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,127 +1476,133 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>22000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>19500</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>700</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-14100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-1100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>9900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>4900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>500</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>200</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>600</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>3200</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>100</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
       <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1587,10 +1610,10 @@
         <v>100</v>
       </c>
       <c r="E15" s="3">
+        <v>100</v>
+      </c>
+      <c r="F15" s="3">
         <v>200</v>
-      </c>
-      <c r="F15" s="3">
-        <v>300</v>
       </c>
       <c r="G15" s="3">
         <v>300</v>
@@ -1599,10 +1622,10 @@
         <v>300</v>
       </c>
       <c r="I15" s="3">
+        <v>300</v>
+      </c>
+      <c r="J15" s="3">
         <v>200</v>
-      </c>
-      <c r="J15" s="3">
-        <v>800</v>
       </c>
       <c r="K15" s="3">
         <v>800</v>
@@ -1629,7 +1652,7 @@
         <v>800</v>
       </c>
       <c r="S15" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="T15" s="3">
         <v>1100</v>
@@ -1647,13 +1670,13 @@
         <v>1100</v>
       </c>
       <c r="Y15" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="Z15" s="3">
         <v>1200</v>
       </c>
       <c r="AA15" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="AB15" s="3">
         <v>1500</v>
@@ -1683,13 +1706,13 @@
         <v>1500</v>
       </c>
       <c r="AK15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AL15" s="3">
         <v>1300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>1700</v>
-      </c>
-      <c r="AM15" s="3">
-        <v>400</v>
       </c>
       <c r="AN15" s="3">
         <v>400</v>
@@ -1697,8 +1720,11 @@
       <c r="AO15" s="3">
         <v>400</v>
       </c>
+      <c r="AP15" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,246 +1763,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E17" s="3">
         <v>20800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>25700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>24700</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>28300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>27500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>29800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>34100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>37100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>38100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>40300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>41700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>38300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>38500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>26100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>38000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>38500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>33800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>32700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>40600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>16000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>37000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>37700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>39200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>41900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>37000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>38500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>38900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>39700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>39800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>43800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>46100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>49500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>21200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>20500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-700</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>-1300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1100</v>
-      </c>
-      <c r="O18" s="3">
-        <v>800</v>
       </c>
       <c r="P18" s="3">
         <v>800</v>
       </c>
       <c r="Q18" s="3">
+        <v>800</v>
+      </c>
+      <c r="R18" s="3">
         <v>-200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>16700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-9600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>10600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-800</v>
       </c>
-      <c r="AF18" s="3">
-        <v>0</v>
-      </c>
       <c r="AG18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="3">
         <v>1000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>300</v>
-      </c>
-      <c r="AN18" s="3">
-        <v>500</v>
       </c>
       <c r="AO18" s="3">
         <v>500</v>
       </c>
+      <c r="AP18" s="3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,17 +2051,18 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>8</v>
       </c>
@@ -2062,8 +2096,8 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -2135,10 +2169,13 @@
         <v>0</v>
       </c>
       <c r="AO20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2146,118 +2183,121 @@
         <v>0</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>-500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1900</v>
-      </c>
-      <c r="O21" s="3">
-        <v>1600</v>
       </c>
       <c r="P21" s="3">
         <v>1600</v>
       </c>
       <c r="Q21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="R21" s="3">
         <v>600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>17800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-8400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>11800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2276,11 +2316,11 @@
       <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="I22" s="3">
         <v>100</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
@@ -2316,25 +2356,25 @@
         <v>100</v>
       </c>
       <c r="V22" s="3">
+        <v>100</v>
+      </c>
+      <c r="W22" s="3">
         <v>500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>3300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>3100</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>3200</v>
       </c>
       <c r="AC22" s="3">
         <v>3200</v>
@@ -2343,278 +2383,287 @@
         <v>3200</v>
       </c>
       <c r="AE22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AF22" s="3">
         <v>3100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>2900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>3100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>2900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>3300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>2900</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>2400</v>
-      </c>
-      <c r="AM22" s="3">
-        <v>400</v>
       </c>
       <c r="AN22" s="3">
         <v>400</v>
       </c>
       <c r="AO22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AP22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
         <v>-200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-23200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-700</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>-20700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1100</v>
-      </c>
-      <c r="O23" s="3">
-        <v>700</v>
       </c>
       <c r="P23" s="3">
         <v>700</v>
       </c>
       <c r="Q23" s="3">
+        <v>700</v>
+      </c>
+      <c r="R23" s="3">
         <v>-300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>16600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>7300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-5800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-100</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F24" s="3">
         <v>-100</v>
       </c>
       <c r="G24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H24" s="3">
         <v>9800</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
         <v>-2500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-900</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-6800</v>
-      </c>
-      <c r="O24" s="3">
-        <v>100</v>
       </c>
       <c r="P24" s="3">
         <v>100</v>
       </c>
       <c r="Q24" s="3">
+        <v>100</v>
+      </c>
+      <c r="R24" s="3">
         <v>500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-100</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-6400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>200</v>
-      </c>
-      <c r="AM24" s="3">
-        <v>100</v>
       </c>
       <c r="AN24" s="3">
         <v>100</v>
       </c>
       <c r="AO24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AP24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
         <v>-200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-33000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-700</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>-18100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7900</v>
-      </c>
-      <c r="O26" s="3">
-        <v>700</v>
       </c>
       <c r="P26" s="3">
         <v>700</v>
       </c>
       <c r="Q26" s="3">
+        <v>700</v>
+      </c>
+      <c r="R26" s="3">
         <v>-800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>16700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-12600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>7200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-5400</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-3600</v>
       </c>
       <c r="AC26" s="3">
         <v>-3600</v>
       </c>
       <c r="AD26" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>-200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-33100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-700</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>-19300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7900</v>
-      </c>
-      <c r="O27" s="3">
-        <v>700</v>
       </c>
       <c r="P27" s="3">
         <v>700</v>
       </c>
       <c r="Q27" s="3">
+        <v>700</v>
+      </c>
+      <c r="R27" s="3">
         <v>-800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>16700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-12600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>31700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-5400</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>-3600</v>
       </c>
       <c r="AC27" s="3">
         <v>-3600</v>
       </c>
       <c r="AD27" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>100</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3098,29 +3159,29 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>100</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-200</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-1200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-100</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
@@ -3163,8 +3224,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3181,21 +3242,21 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>400</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>400</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3208,8 +3269,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,17 +3513,20 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
       </c>
@@ -3490,8 +3560,8 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3563,129 +3633,135 @@
         <v>0</v>
       </c>
       <c r="AO32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
         <v>-200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-33100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-700</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>-19300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7900</v>
-      </c>
-      <c r="O33" s="3">
-        <v>700</v>
       </c>
       <c r="P33" s="3">
         <v>700</v>
       </c>
       <c r="Q33" s="3">
+        <v>700</v>
+      </c>
+      <c r="R33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>16700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-12600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>31700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-5400</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>-3600</v>
       </c>
       <c r="AC33" s="3">
         <v>-3600</v>
       </c>
       <c r="AD33" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>3700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
         <v>-200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-33100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-700</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>-19300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7900</v>
-      </c>
-      <c r="O35" s="3">
-        <v>700</v>
       </c>
       <c r="P35" s="3">
         <v>700</v>
       </c>
       <c r="Q35" s="3">
+        <v>700</v>
+      </c>
+      <c r="R35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>16700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-12600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>31700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-5400</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>-3600</v>
       </c>
       <c r="AC35" s="3">
         <v>-3600</v>
       </c>
       <c r="AD35" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>3700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,127 +4218,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E41" s="3">
         <v>20100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>21400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>22500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>20700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>20100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>18500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>18800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>17500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>14200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>12100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>14300</v>
-      </c>
-      <c r="X41" s="3">
-        <v>14100</v>
       </c>
       <c r="Y41" s="3">
         <v>14100</v>
       </c>
       <c r="Z41" s="3">
+        <v>14100</v>
+      </c>
+      <c r="AA41" s="3">
         <v>16600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4370,55 +4460,58 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E43" s="3">
         <v>8800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>14200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>19900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>20400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>20300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>22800</v>
-      </c>
-      <c r="R43" s="3">
-        <v>21200</v>
       </c>
       <c r="S43" s="3">
         <v>21200</v>
@@ -4427,70 +4520,73 @@
         <v>21200</v>
       </c>
       <c r="U43" s="3">
+        <v>21200</v>
+      </c>
+      <c r="V43" s="3">
         <v>23100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>20300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>19000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>18600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>16000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>13700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>17300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>20200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>20800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>20400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>20000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>19000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>20800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>21200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>20600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>22700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>23200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>24000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>13100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>12600</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4533,8 +4629,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4608,8 +4704,11 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4622,21 +4721,21 @@
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3">
         <v>1200</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>1200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4652,202 +4751,208 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>600</v>
-      </c>
-      <c r="R45" s="3">
-        <v>800</v>
       </c>
       <c r="S45" s="3">
         <v>800</v>
       </c>
       <c r="T45" s="3">
+        <v>800</v>
+      </c>
+      <c r="U45" s="3">
         <v>900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>900</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>1400</v>
       </c>
       <c r="Z45" s="3">
         <v>1400</v>
       </c>
       <c r="AA45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AB45" s="3">
         <v>1600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1600</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E46" s="3">
         <v>29500</v>
-      </c>
-      <c r="E46" s="3">
-        <v>31700</v>
       </c>
       <c r="F46" s="3">
         <v>31700</v>
       </c>
       <c r="G46" s="3">
+        <v>31700</v>
+      </c>
+      <c r="H46" s="3">
         <v>32500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>33000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>35400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>35500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>36800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>37000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>41800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>41400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>41300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>39500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>42200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>39500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>36200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>34200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>33700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>28500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>34700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>33600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>31500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>31700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>21200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>23700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>27100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>27400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>25100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>25000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>26200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>25700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>25300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>27500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>29000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>29400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>16200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>16400</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>15600</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4890,8 +4995,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4965,91 +5070,94 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E48" s="3">
         <v>4000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4600</v>
-      </c>
-      <c r="T48" s="3">
-        <v>4700</v>
       </c>
       <c r="U48" s="3">
         <v>4700</v>
       </c>
       <c r="V48" s="3">
+        <v>4700</v>
+      </c>
+      <c r="W48" s="3">
         <v>4400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5100</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>5500</v>
       </c>
       <c r="Z48" s="3">
         <v>5500</v>
       </c>
       <c r="AA48" s="3">
-        <v>6300</v>
+        <v>5500</v>
       </c>
       <c r="AB48" s="3">
         <v>6300</v>
       </c>
       <c r="AC48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AD48" s="3">
         <v>900</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>800</v>
       </c>
       <c r="AE48" s="3">
         <v>800</v>
@@ -5058,7 +5166,7 @@
         <v>800</v>
       </c>
       <c r="AG48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AH48" s="3">
         <v>900</v>
@@ -5076,16 +5184,19 @@
         <v>900</v>
       </c>
       <c r="AM48" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AN48" s="3">
         <v>500</v>
       </c>
       <c r="AO48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AP48" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5093,118 +5204,121 @@
         <v>25300</v>
       </c>
       <c r="E49" s="3">
+        <v>25300</v>
+      </c>
+      <c r="F49" s="3">
         <v>25400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>25600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>25700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>46600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>46800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>47000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>68300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>69000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>69700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>70400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>71100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>71900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>72600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>73300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>74000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>75000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>78200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>79200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>80200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>81200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>82300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>92300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>93400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>94800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>96200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>97600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>103300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>104700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>106100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>107500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>108900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>110200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>111600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>110300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>28900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>29300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,52 +5558,55 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>100</v>
+      </c>
+      <c r="E52" s="3">
         <v>200</v>
-      </c>
-      <c r="E52" s="3">
-        <v>100</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>200</v>
       </c>
       <c r="I52" s="3">
+        <v>200</v>
+      </c>
+      <c r="J52" s="3">
         <v>600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>500</v>
-      </c>
-      <c r="M52" s="3">
-        <v>600</v>
       </c>
       <c r="N52" s="3">
         <v>600</v>
       </c>
       <c r="O52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="P52" s="3">
         <v>700</v>
       </c>
       <c r="Q52" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="R52" s="3">
         <v>800</v>
@@ -5495,40 +5615,40 @@
         <v>800</v>
       </c>
       <c r="T52" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="U52" s="3">
         <v>1000</v>
       </c>
       <c r="V52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W52" s="3">
         <v>1100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>700</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>300</v>
       </c>
       <c r="AA52" s="3">
         <v>300</v>
       </c>
       <c r="AB52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AC52" s="3">
         <v>400</v>
       </c>
       <c r="AD52" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE52" s="3">
         <v>600</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>400</v>
       </c>
       <c r="AF52" s="3">
         <v>400</v>
@@ -5540,10 +5660,10 @@
         <v>400</v>
       </c>
       <c r="AI52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AJ52" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AK52" s="3">
         <v>300</v>
@@ -5552,7 +5672,7 @@
         <v>300</v>
       </c>
       <c r="AM52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AN52" s="3">
         <v>0</v>
@@ -5560,8 +5680,11 @@
       <c r="AO52" s="3">
         <v>0</v>
       </c>
+      <c r="AP52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E54" s="3">
         <v>58900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>60000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>60600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>61800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>92800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>95900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>96900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>117000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>117600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>123600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>123700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>118100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>116200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>119600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>117800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>115600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>114900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>117600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>113300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>120200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>120500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>120000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>129800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>121200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>125200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>124500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>126300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>129600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>130900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>133600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>134400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>135100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>139000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>141800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>141000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>45700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>46300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>45900</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,135 +6014,139 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100</v>
-      </c>
-      <c r="E57" s="3">
-        <v>1400</v>
       </c>
       <c r="F57" s="3">
         <v>1400</v>
       </c>
       <c r="G57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H57" s="3">
         <v>1900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2400</v>
-      </c>
-      <c r="K57" s="3">
-        <v>2500</v>
       </c>
       <c r="L57" s="3">
         <v>2500</v>
       </c>
       <c r="M57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N57" s="3">
         <v>2800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2500</v>
-      </c>
-      <c r="AH57" s="3">
-        <v>2000</v>
       </c>
       <c r="AI57" s="3">
         <v>2000</v>
       </c>
       <c r="AJ57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AK57" s="3">
         <v>2100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E58" s="3">
         <v>1100</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1300</v>
       </c>
       <c r="F58" s="3">
         <v>1300</v>
@@ -6021,35 +6155,35 @@
         <v>1300</v>
       </c>
       <c r="H58" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="I58" s="3">
         <v>1200</v>
       </c>
       <c r="J58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K58" s="3">
         <v>1300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1400</v>
-      </c>
-      <c r="L58" s="3">
-        <v>1500</v>
       </c>
       <c r="M58" s="3">
         <v>1500</v>
       </c>
       <c r="N58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O58" s="3">
         <v>1700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1300</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6060,353 +6194,362 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>16700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>11000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>8800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7900</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
       <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
         <v>1200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>5700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>17200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>16800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>15000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>12600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>14000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>8500</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>10100</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100</v>
+      </c>
+      <c r="E59" s="3">
         <v>200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>800</v>
       </c>
       <c r="G59" s="3">
         <v>800</v>
       </c>
       <c r="H59" s="3">
+        <v>800</v>
+      </c>
+      <c r="I59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>12200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>14600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>13900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>8600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>9800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>13800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>12500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>5000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>4800</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E60" s="3">
         <v>5500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>15600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>31200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>23400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>26000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>22100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>18200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>24800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>11700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>13400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>18600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>15900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>14000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>13500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>13100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>27800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>26300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>26900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>19500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>27900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>14800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>16400</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E61" s="3">
         <v>3200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2500</v>
-      </c>
-      <c r="N61" s="3">
-        <v>3100</v>
       </c>
       <c r="O61" s="3">
         <v>3100</v>
       </c>
       <c r="P61" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Q61" s="3">
         <v>2000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -6420,67 +6563,70 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>7000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>62500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>65000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>67400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>60700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>74900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>72500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>68200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>69800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>69900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>68800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>69900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>55000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>56000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>58500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>67600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>59000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>4900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>4800</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6499,11 +6645,11 @@
       <c r="H62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>8</v>
@@ -6511,59 +6657,59 @@
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3">
         <v>400</v>
-      </c>
-      <c r="N62" s="3">
-        <v>200</v>
       </c>
       <c r="O62" s="3">
         <v>200</v>
       </c>
       <c r="P62" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q62" s="3">
         <v>500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4600</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>4900</v>
       </c>
       <c r="AB62" s="3">
         <v>4900</v>
       </c>
       <c r="AC62" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AD62" s="3">
         <v>900</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>1200</v>
       </c>
       <c r="AE62" s="3">
         <v>1200</v>
@@ -6572,25 +6718,25 @@
         <v>1200</v>
       </c>
       <c r="AG62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AH62" s="3">
         <v>700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>4700</v>
-      </c>
-      <c r="AM62" s="3">
-        <v>200</v>
       </c>
       <c r="AN62" s="3">
         <v>200</v>
@@ -6598,8 +6744,11 @@
       <c r="AO62" s="3">
         <v>200</v>
       </c>
+      <c r="AP62" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E66" s="3">
         <v>9000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>17300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>36800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>35600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>94300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>93100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>92600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>90100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>91500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>90900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>87700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>86900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>85100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>83500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>83700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>84500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>84100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>86500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>88400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>91600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>19800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>21500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7430,13 +7598,13 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
-        <v>27700</v>
+        <v>0</v>
       </c>
       <c r="AB70" s="3">
         <v>27700</v>
       </c>
       <c r="AC70" s="3">
-        <v>27600</v>
+        <v>27700</v>
       </c>
       <c r="AD70" s="3">
         <v>27600</v>
@@ -7448,7 +7616,7 @@
         <v>27600</v>
       </c>
       <c r="AG70" s="3">
-        <v>28800</v>
+        <v>27600</v>
       </c>
       <c r="AH70" s="3">
         <v>28800</v>
@@ -7457,7 +7625,7 @@
         <v>28800</v>
       </c>
       <c r="AJ70" s="3">
-        <v>29300</v>
+        <v>28800</v>
       </c>
       <c r="AK70" s="3">
         <v>29300</v>
@@ -7466,7 +7634,7 @@
         <v>29300</v>
       </c>
       <c r="AM70" s="3">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="AN70" s="3">
         <v>0</v>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,8 +7764,11 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7602,118 +7776,121 @@
         <v>-60600</v>
       </c>
       <c r="E72" s="3">
+        <v>-60600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-60500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-60000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-59500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-26400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-25700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-23500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-4200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-9700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-10400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-11000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-10300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-12900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-14000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-30600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-33600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-32700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-31000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-30700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-18100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-49800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-44300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-40800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-37200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-30400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-26500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-23000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-22000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-20100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-17200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-15500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-19200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-13200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-13000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,8 +8252,11 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -8081,115 +8267,118 @@
         <v>50000</v>
       </c>
       <c r="F76" s="3">
+        <v>50000</v>
+      </c>
+      <c r="G76" s="3">
         <v>50400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>50600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>83600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>84200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>86300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>105500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>106300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>109300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>110400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>102800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>102000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>101000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>101600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>98800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>97600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>80800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>77600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>25900</v>
-      </c>
-      <c r="X76" s="3">
-        <v>27400</v>
       </c>
       <c r="Y76" s="3">
         <v>27400</v>
       </c>
       <c r="Z76" s="3">
+        <v>27400</v>
+      </c>
+      <c r="AA76" s="3">
         <v>39700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>16900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>19900</v>
-      </c>
-      <c r="AG76" s="3">
-        <v>21100</v>
       </c>
       <c r="AH76" s="3">
         <v>21100</v>
       </c>
       <c r="AI76" s="3">
+        <v>21100</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>22200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>23200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>24100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>20100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>25800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>24800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
         <v>-200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-33100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-700</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>-19300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7900</v>
-      </c>
-      <c r="O81" s="3">
-        <v>700</v>
       </c>
       <c r="P81" s="3">
         <v>700</v>
       </c>
       <c r="Q81" s="3">
+        <v>700</v>
+      </c>
+      <c r="R81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>16700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-12600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>31700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-5400</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>-3600</v>
       </c>
       <c r="AC81" s="3">
         <v>-3600</v>
       </c>
       <c r="AD81" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>3700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,19 +8791,20 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>400</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="E83" s="3">
         <v>400</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G83" s="3">
         <v>400</v>
@@ -8617,10 +8816,10 @@
         <v>400</v>
       </c>
       <c r="J83" s="3">
+        <v>400</v>
+      </c>
+      <c r="K83" s="3">
         <v>1100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>100</v>
       </c>
       <c r="L83" s="3">
         <v>100</v>
@@ -8638,13 +8837,13 @@
         <v>100</v>
       </c>
       <c r="Q83" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>800</v>
       </c>
       <c r="S83" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="T83" s="3">
         <v>1100</v>
@@ -8662,13 +8861,13 @@
         <v>1100</v>
       </c>
       <c r="Y83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="Z83" s="3">
         <v>1200</v>
       </c>
       <c r="AA83" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="AB83" s="3">
         <v>1500</v>
@@ -8698,13 +8897,13 @@
         <v>1500</v>
       </c>
       <c r="AK83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AL83" s="3">
         <v>1300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1700</v>
-      </c>
-      <c r="AM83" s="3">
-        <v>400</v>
       </c>
       <c r="AN83" s="3">
         <v>400</v>
@@ -8712,8 +8911,11 @@
       <c r="AO83" s="3">
         <v>400</v>
       </c>
+      <c r="AP83" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1200</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>-1100</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
         <v>-1500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>100</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-600</v>
-      </c>
-      <c r="AF89" s="3">
-        <v>800</v>
       </c>
       <c r="AG89" s="3">
         <v>800</v>
       </c>
       <c r="AH89" s="3">
+        <v>800</v>
+      </c>
+      <c r="AI89" s="3">
         <v>500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,19 +9689,20 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -9489,11 +9710,11 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -9511,7 +9732,7 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>-100</v>
@@ -9532,7 +9753,7 @@
         <v>-100</v>
       </c>
       <c r="W91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -9547,13 +9768,13 @@
         <v>0</v>
       </c>
       <c r="AB91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC91" s="3">
         <v>-100</v>
       </c>
       <c r="AD91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
@@ -9562,23 +9783,23 @@
         <v>0</v>
       </c>
       <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-100</v>
       </c>
-      <c r="AH91" s="3">
-        <v>0</v>
-      </c>
       <c r="AI91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AJ91" s="3">
         <v>-100</v>
       </c>
       <c r="AK91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-200</v>
       </c>
-      <c r="AL91" s="3">
-        <v>0</v>
-      </c>
       <c r="AM91" s="3">
         <v>0</v>
       </c>
@@ -9586,10 +9807,13 @@
         <v>0</v>
       </c>
       <c r="AO91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,31 +10053,34 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3">
         <v>700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1000</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -9868,7 +10098,7 @@
         <v>0</v>
       </c>
       <c r="P94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q94" s="3">
         <v>-100</v>
@@ -9889,7 +10119,7 @@
         <v>-100</v>
       </c>
       <c r="W94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -9904,13 +10134,13 @@
         <v>0</v>
       </c>
       <c r="AB94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC94" s="3">
         <v>-100</v>
       </c>
       <c r="AD94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE94" s="3">
         <v>0</v>
@@ -9919,34 +10149,37 @@
         <v>0</v>
       </c>
       <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-100</v>
       </c>
-      <c r="AH94" s="3">
-        <v>0</v>
-      </c>
       <c r="AI94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AJ94" s="3">
         <v>-100</v>
       </c>
       <c r="AK94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-24800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-500</v>
-      </c>
-      <c r="AN94" s="3">
-        <v>-100</v>
       </c>
       <c r="AO94" s="3">
         <v>-100</v>
       </c>
+      <c r="AP94" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,8 +10221,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10032,8 +10266,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10107,8 +10341,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,19 +10707,22 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
         <v>0</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G100" s="3">
         <v>0</v>
@@ -10484,30 +10730,30 @@
       <c r="H100" s="3">
         <v>0</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
-        <v>-1600</v>
+        <v>0</v>
       </c>
       <c r="M100" s="3">
         <v>-1600</v>
       </c>
       <c r="N100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="O100" s="3">
         <v>-500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
@@ -10524,11 +10770,11 @@
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-4400</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
@@ -10536,55 +10782,58 @@
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>11900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>26700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10627,8 +10876,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10702,123 +10951,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1200</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1100</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>100</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>14200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-1000</v>
       </c>
     </row>
